--- a/extras/DigitalFilter/DigitalFilter.xlsx
+++ b/extras/DigitalFilter/DigitalFilter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_\cloud\hugo\Arduino\libraries\madflight\extras\DigitalFilter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E91DA3C-B93C-4D32-A868-29721E23C803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2765F89F-B61E-4074-80D8-C5BF7493B729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{D8145382-1E42-40AB-968A-D64BBFD22769}"/>
   </bookViews>
@@ -34,9 +34,6 @@
   </si>
   <si>
     <t>Digital Filter</t>
-  </si>
-  <si>
-    <t>Out(i)=Out(i)−1+β(Sample(i)−Output(i−1))</t>
   </si>
   <si>
     <t>i</t>
@@ -95,15 +92,19 @@
   <si>
     <t>Input Frequency:</t>
   </si>
+  <si>
+    <t>Out(i)=Out(i)−1+β(Sample(i)−Out(i−1))</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.000"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,6 +124,13 @@
       <b/>
       <sz val="16"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -154,12 +162,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -282,8 +293,11 @@
             <c:numRef>
               <c:f>Sheet1!$B$14:$B$115</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="102"/>
+                <c:pt idx="0">
+                  <c:v>-1</c:v>
+                </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
@@ -596,6 +610,9 @@
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="102"/>
+                <c:pt idx="0">
+                  <c:v>-0.12533323356430426</c:v>
+                </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
@@ -939,8 +956,11 @@
             <c:numRef>
               <c:f>Sheet1!$B$14:$B$115</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="102"/>
+                <c:pt idx="0">
+                  <c:v>-1</c:v>
+                </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1584,6 +1604,7 @@
         <c:axId val="471394632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1601,7 +1622,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1892,8 +1913,11 @@
             <c:numRef>
               <c:f>Sheet1!$B$14:$B$115</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="102"/>
+                <c:pt idx="0">
+                  <c:v>-1</c:v>
+                </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2206,6 +2230,9 @@
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="102"/>
+                <c:pt idx="0">
+                  <c:v>-0.12533323356430426</c:v>
+                </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2563,8 +2590,11 @@
             <c:numRef>
               <c:f>Sheet1!$B$14:$B$115</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="102"/>
+                <c:pt idx="0">
+                  <c:v>-1</c:v>
+                </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2877,11 +2907,8 @@
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="102"/>
-                <c:pt idx="0" formatCode="General">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>125.33323356430427</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>125.33323356430427</c:v>
@@ -3223,8 +3250,11 @@
             <c:numRef>
               <c:f>Sheet1!$B$14:$B$115</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="102"/>
+                <c:pt idx="0">
+                  <c:v>-1</c:v>
+                </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3537,9 +3567,6 @@
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="102"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3883,8 +3910,11 @@
             <c:numRef>
               <c:f>Sheet1!$B$14:$B$115</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="102"/>
+                <c:pt idx="0">
+                  <c:v>-1</c:v>
+                </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4528,6 +4558,7 @@
         <c:axId val="474321560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -4545,7 +4576,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4703,11 +4734,12 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="848721544"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -5910,15 +5942,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>54428</xdr:colOff>
+      <xdr:colOff>484413</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>46263</xdr:rowOff>
+      <xdr:rowOff>51704</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>304799</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>92527</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>122463</xdr:rowOff>
+      <xdr:rowOff>127904</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5946,15 +5978,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>57148</xdr:colOff>
+      <xdr:colOff>487134</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>133351</xdr:rowOff>
+      <xdr:rowOff>127907</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>293914</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>81644</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>100694</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6279,170 +6311,188 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3BE3B55-CFBA-4A3C-BC6D-3235A7EDF167}">
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:K115"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="1" max="1" width="4.84375" customWidth="1"/>
     <col min="2" max="4" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="9.3828125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11" ht="20.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="4">
         <v>1000</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="4">
         <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="4">
         <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="4">
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="4">
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" s="1">
         <f>1-EXP(-2*PI()*D5/D4)</f>
         <v>0.31407783406583367</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" s="1">
         <f>1-EXP(-2*PI()*D6/D4)</f>
         <v>0.31407783406583367</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="J12" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="I12" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>14</v>
+      <c r="I13" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L13" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>-1</v>
+      </c>
+      <c r="B14" s="5">
+        <f>A14/$D$4*1000</f>
+        <v>-1</v>
+      </c>
+      <c r="C14" s="1">
+        <f>INDEX(I14:K14,1,$D$7)</f>
+        <v>-0.12533323356430426</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <f>IF(MOD(A14,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <f>IF(MOD(A14,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <f>SIN(2*PI()*B14/$D$4*$D$8)</f>
+        <v>-0.12533323356430426</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>0</v>
       </c>
-      <c r="B15">
-        <f>A15/$D$4*1000</f>
+      <c r="B15" s="5">
+        <f t="shared" ref="B15:B78" si="0">A15/$D$4*1000</f>
         <v>0</v>
       </c>
       <c r="C15" s="1">
-        <f>INDEX(J15:L15,1,$D$7)</f>
+        <f>INDEX(I15:K15,1,$D$7)</f>
         <v>0</v>
       </c>
       <c r="D15" s="1">
-        <f>D14+$D$10*(C15-D14)</f>
+        <f t="shared" ref="D15:D46" si="1">D14+$D$10*(C15-D14)</f>
         <v>0</v>
       </c>
       <c r="E15" s="1">
         <f>(C15-C14)*1000</f>
-        <v>0</v>
+        <v>125.33323356430427</v>
       </c>
       <c r="F15" s="1">
         <f>(D15-D14)*1000</f>
@@ -6452,4020 +6502,4020 @@
         <f>G14+$D$11*(F15-G14)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="1">
+      <c r="I15" s="1">
         <f>IF(MOD(A15,FLOOR($D$4/$D$8,1))=0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K15" s="1">
+      <c r="J15" s="1">
         <f>IF(MOD(A15,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
         <v>1</v>
       </c>
-      <c r="L15" s="1">
-        <f>SIN(2*PI()*B15/$D$4*$D$8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="K15" s="1">
+        <f t="shared" ref="K15:K78" si="2">SIN(2*PI()*B15/$D$4*$D$8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16">
-        <f t="shared" ref="A16:A79" si="0">A15+1</f>
+        <f t="shared" ref="A16:A79" si="3">A15+1</f>
         <v>1</v>
       </c>
-      <c r="B16">
-        <f>A16/$D$4*1000</f>
+      <c r="B16" s="5">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C16" s="1">
-        <f>INDEX(J16:L16,1,$D$7)</f>
+        <f>INDEX(I16:K16,1,$D$7)</f>
         <v>0.12533323356430426</v>
       </c>
       <c r="D16" s="1">
-        <f>D15+$D$10*(C16-D15)</f>
+        <f t="shared" si="1"/>
         <v>3.9364390534343929E-2</v>
       </c>
       <c r="E16" s="1">
-        <f t="shared" ref="E16:E79" si="1">(C16-C15)*1000</f>
+        <f t="shared" ref="E16:E79" si="4">(C16-C15)*1000</f>
         <v>125.33323356430427</v>
       </c>
       <c r="F16" s="1">
-        <f>(D16-D15)*1000</f>
+        <f t="shared" ref="F16:F47" si="5">(D16-D15)*1000</f>
         <v>39.364390534343926</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" ref="G16:G79" si="2">G15+$D$11*(F16-G15)</f>
+        <f t="shared" ref="G16:G79" si="6">G15+$D$11*(F16-G15)</f>
         <v>12.363482518348345</v>
       </c>
+      <c r="I16" s="1">
+        <f>IF(MOD(A16,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
       <c r="J16" s="1">
-        <f t="shared" ref="J16:J79" si="3">IF(MOD(A16,FLOOR($D$4/$D$8,1))=0,1,0)</f>
-        <v>0</v>
+        <f>IF(MOD(A16,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <f t="shared" ref="K16:K79" si="4">IF(MOD(A16,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="L16" s="1">
-        <f>SIN(2*PI()*B16/$D$4*$D$8)</f>
+        <f t="shared" si="2"/>
         <v>0.12533323356430426</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="B17" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B17">
-        <f>A17/$D$4*1000</f>
-        <v>2</v>
-      </c>
       <c r="C17" s="1">
-        <f>INDEX(J17:L17,1,$D$7)</f>
+        <f>INDEX(I17:K17,1,$D$7)</f>
         <v>0.24868988716485479</v>
       </c>
       <c r="D17" s="1">
-        <f>D16+$D$10*(C17-D16)</f>
+        <f t="shared" si="1"/>
         <v>0.10510888913080975</v>
       </c>
       <c r="E17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>123.35665360055053</v>
       </c>
       <c r="F17" s="1">
-        <f>(D17-D16)*1000</f>
+        <f t="shared" si="5"/>
         <v>65.744498596465817</v>
       </c>
       <c r="G17" s="1">
+        <f t="shared" si="6"/>
+        <v>29.129276428396924</v>
+      </c>
+      <c r="I17" s="1">
+        <f>IF(MOD(A17,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <f>IF(MOD(A17,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K17" s="1">
         <f t="shared" si="2"/>
-        <v>29.129276428396924</v>
-      </c>
-      <c r="J17" s="1">
+        <v>0.24868988716485479</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A18">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L17" s="1">
-        <f>SIN(2*PI()*B17/$D$4*$D$8)</f>
-        <v>0.24868988716485479</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B18">
-        <f>A18/$D$4*1000</f>
-        <v>3</v>
-      </c>
       <c r="C18" s="1">
-        <f>INDEX(J18:L18,1,$D$7)</f>
+        <f>INDEX(I18:K18,1,$D$7)</f>
         <v>0.36812455268467792</v>
       </c>
       <c r="D18" s="1">
-        <f>D17+$D$10*(C18-D17)</f>
+        <f t="shared" si="1"/>
         <v>0.1877162790651967</v>
       </c>
       <c r="E18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>119.43466551982313</v>
       </c>
       <c r="F18" s="1">
-        <f>(D18-D17)*1000</f>
+        <f t="shared" si="5"/>
         <v>82.607389934386944</v>
       </c>
       <c r="G18" s="1">
+        <f t="shared" si="6"/>
+        <v>45.925566488285078</v>
+      </c>
+      <c r="I18" s="1">
+        <f>IF(MOD(A18,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <f>IF(MOD(A18,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K18" s="1">
         <f t="shared" si="2"/>
-        <v>45.925566488285078</v>
-      </c>
-      <c r="J18" s="1">
+        <v>0.36812455268467792</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A19">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L18" s="1">
-        <f>SIN(2*PI()*B18/$D$4*$D$8)</f>
-        <v>0.36812455268467792</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A19">
+        <v>4</v>
+      </c>
+      <c r="B19" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B19">
-        <f>A19/$D$4*1000</f>
-        <v>4</v>
-      </c>
       <c r="C19" s="1">
-        <f>INDEX(J19:L19,1,$D$7)</f>
+        <f>INDEX(I19:K19,1,$D$7)</f>
         <v>0.48175367410171532</v>
       </c>
       <c r="D19" s="1">
-        <f>D18+$D$10*(C19-D18)</f>
+        <f t="shared" si="1"/>
         <v>0.28006690723262639</v>
       </c>
       <c r="E19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>113.62912141703741</v>
       </c>
       <c r="F19" s="1">
-        <f>(D19-D18)*1000</f>
+        <f t="shared" si="5"/>
         <v>92.350628167429704</v>
       </c>
       <c r="G19" s="1">
+        <f t="shared" si="6"/>
+        <v>60.506649306843556</v>
+      </c>
+      <c r="I19" s="1">
+        <f>IF(MOD(A19,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <f>IF(MOD(A19,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
         <f t="shared" si="2"/>
-        <v>60.506649306843556</v>
-      </c>
-      <c r="J19" s="1">
+        <v>0.48175367410171532</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L19" s="1">
-        <f>SIN(2*PI()*B19/$D$4*$D$8)</f>
-        <v>0.48175367410171532</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B20">
-        <f>A20/$D$4*1000</f>
-        <v>5</v>
-      </c>
       <c r="C20" s="1">
-        <f>INDEX(J20:L20,1,$D$7)</f>
+        <f>INDEX(I20:K20,1,$D$7)</f>
         <v>0.58778525229247314</v>
       </c>
       <c r="D20" s="1">
-        <f>D19+$D$10*(C20-D19)</f>
+        <f t="shared" si="1"/>
         <v>0.37671441855134591</v>
       </c>
       <c r="E20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>106.03157819075781</v>
       </c>
       <c r="F20" s="1">
-        <f>(D20-D19)*1000</f>
+        <f t="shared" si="5"/>
         <v>96.647511318719509</v>
       </c>
       <c r="G20" s="1">
+        <f t="shared" si="6"/>
+        <v>71.857692968805722</v>
+      </c>
+      <c r="I20" s="1">
+        <f>IF(MOD(A20,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <f>IF(MOD(A20,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K20" s="1">
         <f t="shared" si="2"/>
-        <v>71.857692968805722</v>
-      </c>
-      <c r="J20" s="1">
+        <v>0.58778525229247314</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A21">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L20" s="1">
-        <f>SIN(2*PI()*B20/$D$4*$D$8)</f>
-        <v>0.58778525229247314</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A21">
+        <v>6</v>
+      </c>
+      <c r="B21" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B21">
-        <f>A21/$D$4*1000</f>
-        <v>6</v>
-      </c>
       <c r="C21" s="1">
-        <f>INDEX(J21:L21,1,$D$7)</f>
+        <f>INDEX(I21:K21,1,$D$7)</f>
         <v>0.68454710592868862</v>
       </c>
       <c r="D21" s="1">
-        <f>D20+$D$10*(C21-D20)</f>
+        <f t="shared" si="1"/>
         <v>0.4733978422574866</v>
       </c>
       <c r="E21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>96.761853636215477</v>
       </c>
       <c r="F21" s="1">
-        <f>(D21-D20)*1000</f>
+        <f t="shared" si="5"/>
         <v>96.683423706140687</v>
       </c>
       <c r="G21" s="1">
+        <f t="shared" si="6"/>
+        <v>79.654904707889486</v>
+      </c>
+      <c r="I21" s="1">
+        <f>IF(MOD(A21,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <f>IF(MOD(A21,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K21" s="1">
         <f t="shared" si="2"/>
-        <v>79.654904707889486</v>
-      </c>
-      <c r="J21" s="1">
+        <v>0.68454710592868862</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A22">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L21" s="1">
-        <f>SIN(2*PI()*B21/$D$4*$D$8)</f>
-        <v>0.68454710592868862</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A22">
+        <v>7</v>
+      </c>
+      <c r="B22" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B22">
-        <f>A22/$D$4*1000</f>
-        <v>7</v>
-      </c>
       <c r="C22" s="1">
-        <f>INDEX(J22:L22,1,$D$7)</f>
+        <f>INDEX(I22:K22,1,$D$7)</f>
         <v>0.77051324277578914</v>
       </c>
       <c r="D22" s="1">
-        <f>D21+$D$10*(C22-D21)</f>
+        <f t="shared" si="1"/>
         <v>0.56671520371987771</v>
       </c>
       <c r="E22" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>85.966136847100529</v>
       </c>
       <c r="F22" s="1">
-        <f>(D22-D21)*1000</f>
+        <f t="shared" si="5"/>
         <v>93.317361462391119</v>
       </c>
       <c r="G22" s="1">
+        <f t="shared" si="6"/>
+        <v>83.945979533361481</v>
+      </c>
+      <c r="I22" s="1">
+        <f>IF(MOD(A22,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <f>IF(MOD(A22,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
         <f t="shared" si="2"/>
-        <v>83.945979533361481</v>
-      </c>
-      <c r="J22" s="1">
+        <v>0.77051324277578914</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A23">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L22" s="1">
-        <f>SIN(2*PI()*B22/$D$4*$D$8)</f>
-        <v>0.77051324277578914</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A23">
+        <v>8</v>
+      </c>
+      <c r="B23" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B23">
-        <f>A23/$D$4*1000</f>
-        <v>8</v>
-      </c>
       <c r="C23" s="1">
-        <f>INDEX(J23:L23,1,$D$7)</f>
+        <f>INDEX(I23:K23,1,$D$7)</f>
         <v>0.84432792550201508</v>
       </c>
       <c r="D23" s="1">
-        <f>D22+$D$10*(C23-D22)</f>
+        <f t="shared" si="1"/>
         <v>0.65390720608633235</v>
       </c>
       <c r="E23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>73.814682726225939</v>
       </c>
       <c r="F23" s="1">
-        <f>(D23-D22)*1000</f>
+        <f t="shared" si="5"/>
         <v>87.192002366454631</v>
       </c>
       <c r="G23" s="1">
+        <f t="shared" si="6"/>
+        <v>84.965483354107619</v>
+      </c>
+      <c r="I23" s="1">
+        <f>IF(MOD(A23,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <f>IF(MOD(A23,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K23" s="1">
         <f t="shared" si="2"/>
-        <v>84.965483354107619</v>
-      </c>
-      <c r="J23" s="1">
+        <v>0.84432792550201508</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A24">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L23" s="1">
-        <f>SIN(2*PI()*B23/$D$4*$D$8)</f>
-        <v>0.84432792550201508</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A24">
+        <v>9</v>
+      </c>
+      <c r="B24" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B24">
-        <f>A24/$D$4*1000</f>
-        <v>9</v>
-      </c>
       <c r="C24" s="1">
-        <f>INDEX(J24:L24,1,$D$7)</f>
+        <f>INDEX(I24:K24,1,$D$7)</f>
         <v>0.90482705246601958</v>
       </c>
       <c r="D24" s="1">
-        <f>D23+$D$10*(C24-D23)</f>
+        <f t="shared" si="1"/>
         <v>0.73271556796139625</v>
       </c>
       <c r="E24" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>60.499126964004503</v>
       </c>
       <c r="F24" s="1">
-        <f>(D24-D23)*1000</f>
+        <f t="shared" si="5"/>
         <v>78.808361875063909</v>
       </c>
       <c r="G24" s="1">
+        <f t="shared" si="6"/>
+        <v>83.031667975889349</v>
+      </c>
+      <c r="I24" s="1">
+        <f>IF(MOD(A24,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <f>IF(MOD(A24,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K24" s="1">
         <f t="shared" si="2"/>
-        <v>83.031667975889349</v>
-      </c>
-      <c r="J24" s="1">
+        <v>0.90482705246601958</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L24" s="1">
-        <f>SIN(2*PI()*B24/$D$4*$D$8)</f>
-        <v>0.90482705246601958</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A25">
+        <v>10</v>
+      </c>
+      <c r="B25" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B25">
-        <f>A25/$D$4*1000</f>
-        <v>10</v>
-      </c>
       <c r="C25" s="1">
-        <f>INDEX(J25:L25,1,$D$7)</f>
+        <f>INDEX(I25:K25,1,$D$7)</f>
         <v>0.95105651629515353</v>
       </c>
       <c r="D25" s="1">
-        <f>D24+$D$10*(C25-D24)</f>
+        <f t="shared" si="1"/>
         <v>0.80129162010194288</v>
       </c>
       <c r="E25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>46.229463829133955</v>
       </c>
       <c r="F25" s="1">
-        <f>(D25-D24)*1000</f>
+        <f t="shared" si="5"/>
         <v>68.576052140546622</v>
       </c>
       <c r="G25" s="1">
+        <f t="shared" si="6"/>
+        <v>78.491479464237145</v>
+      </c>
+      <c r="I25" s="1">
+        <f>IF(MOD(A25,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <f>IF(MOD(A25,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K25" s="1">
         <f t="shared" si="2"/>
-        <v>78.491479464237145</v>
-      </c>
-      <c r="J25" s="1">
+        <v>0.95105651629515353</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A26">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L25" s="1">
-        <f>SIN(2*PI()*B25/$D$4*$D$8)</f>
-        <v>0.95105651629515353</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A26">
+        <v>11</v>
+      </c>
+      <c r="B26" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B26">
-        <f>A26/$D$4*1000</f>
-        <v>11</v>
-      </c>
       <c r="C26" s="1">
-        <f>INDEX(J26:L26,1,$D$7)</f>
+        <f>INDEX(I26:K26,1,$D$7)</f>
         <v>0.98228725072868861</v>
       </c>
       <c r="D26" s="1">
-        <f>D25+$D$10*(C26-D25)</f>
+        <f t="shared" si="1"/>
         <v>0.85813833574457088</v>
       </c>
       <c r="E26" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>31.23073443353508</v>
       </c>
       <c r="F26" s="1">
-        <f>(D26-D25)*1000</f>
+        <f t="shared" si="5"/>
         <v>56.846715642627998</v>
       </c>
       <c r="G26" s="1">
+        <f t="shared" si="6"/>
+        <v>71.69333892427963</v>
+      </c>
+      <c r="I26" s="1">
+        <f>IF(MOD(A26,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <f>IF(MOD(A26,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K26" s="1">
         <f t="shared" si="2"/>
-        <v>71.69333892427963</v>
-      </c>
-      <c r="J26" s="1">
+        <v>0.98228725072868861</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A27">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L26" s="1">
-        <f>SIN(2*PI()*B26/$D$4*$D$8)</f>
-        <v>0.98228725072868861</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A27">
+        <v>12</v>
+      </c>
+      <c r="B27" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B27">
-        <f>A27/$D$4*1000</f>
-        <v>12</v>
-      </c>
       <c r="C27" s="1">
-        <f>INDEX(J27:L27,1,$D$7)</f>
+        <f>INDEX(I27:K27,1,$D$7)</f>
         <v>0.99802672842827156</v>
       </c>
       <c r="D27" s="1">
-        <f>D26+$D$10*(C27-D26)</f>
+        <f t="shared" si="1"/>
         <v>0.9020741791296184</v>
       </c>
       <c r="E27" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>15.739477699582949</v>
       </c>
       <c r="F27" s="1">
-        <f>(D27-D26)*1000</f>
+        <f t="shared" si="5"/>
         <v>43.935843385047527</v>
       </c>
       <c r="G27" s="1">
+        <f t="shared" si="6"/>
+        <v>62.975324846225568</v>
+      </c>
+      <c r="I27" s="1">
+        <f>IF(MOD(A27,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <f>IF(MOD(A27,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
         <f t="shared" si="2"/>
-        <v>62.975324846225568</v>
-      </c>
-      <c r="J27" s="1">
+        <v>0.99802672842827156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L27" s="1">
-        <f>SIN(2*PI()*B27/$D$4*$D$8)</f>
-        <v>0.99802672842827156</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A28">
+        <v>13</v>
+      </c>
+      <c r="B28" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B28">
-        <f>A28/$D$4*1000</f>
-        <v>13</v>
-      </c>
       <c r="C28" s="1">
-        <f>INDEX(J28:L28,1,$D$7)</f>
+        <f>INDEX(I28:K28,1,$D$7)</f>
         <v>0.99802672842827156</v>
       </c>
       <c r="D28" s="1">
-        <f>D27+$D$10*(C28-D27)</f>
+        <f t="shared" si="1"/>
         <v>0.93221074798643455</v>
       </c>
       <c r="E28" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F28" s="1">
-        <f>(D28-D27)*1000</f>
+        <f t="shared" si="5"/>
         <v>30.136568856816147</v>
       </c>
       <c r="G28" s="1">
+        <f t="shared" si="6"/>
+        <v>52.66139949165543</v>
+      </c>
+      <c r="I28" s="1">
+        <f>IF(MOD(A28,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <f>IF(MOD(A28,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K28" s="1">
         <f t="shared" si="2"/>
-        <v>52.66139949165543</v>
-      </c>
-      <c r="J28" s="1">
+        <v>0.99802672842827156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A29">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L28" s="1">
-        <f>SIN(2*PI()*B28/$D$4*$D$8)</f>
-        <v>0.99802672842827156</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A29">
+        <v>14</v>
+      </c>
+      <c r="B29" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B29">
-        <f>A29/$D$4*1000</f>
-        <v>14</v>
-      </c>
       <c r="C29" s="1">
-        <f>INDEX(J29:L29,1,$D$7)</f>
+        <f>INDEX(I29:K29,1,$D$7)</f>
         <v>0.98228725072868872</v>
       </c>
       <c r="D29" s="1">
-        <f>D28+$D$10*(C29-D28)</f>
+        <f t="shared" si="1"/>
         <v>0.94793866750531353</v>
       </c>
       <c r="E29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-15.739477699582839</v>
       </c>
       <c r="F29" s="1">
-        <f>(D29-D28)*1000</f>
+        <f t="shared" si="5"/>
         <v>15.727919518878974</v>
       </c>
       <c r="G29" s="1">
+        <f t="shared" si="6"/>
+        <v>41.061412097291957</v>
+      </c>
+      <c r="I29" s="1">
+        <f>IF(MOD(A29,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="1">
+        <f>IF(MOD(A29,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K29" s="1">
         <f t="shared" si="2"/>
-        <v>41.061412097291957</v>
-      </c>
-      <c r="J29" s="1">
+        <v>0.98228725072868872</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A30">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L29" s="1">
-        <f>SIN(2*PI()*B29/$D$4*$D$8)</f>
-        <v>0.98228725072868872</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A30">
+        <v>15</v>
+      </c>
+      <c r="B30" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B30">
-        <f>A30/$D$4*1000</f>
-        <v>15</v>
-      </c>
       <c r="C30" s="1">
-        <f>INDEX(J30:L30,1,$D$7)</f>
+        <f>INDEX(I30:K30,1,$D$7)</f>
         <v>0.95105651629515364</v>
       </c>
       <c r="D30" s="1">
-        <f>D29+$D$10*(C30-D29)</f>
+        <f t="shared" si="1"/>
         <v>0.94891791470017128</v>
       </c>
       <c r="E30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-31.23073443353508</v>
       </c>
       <c r="F30" s="1">
-        <f>(D30-D29)*1000</f>
+        <f t="shared" si="5"/>
         <v>0.97924719485775746</v>
       </c>
       <c r="G30" s="1">
+        <f t="shared" si="6"/>
+        <v>28.472492560065845</v>
+      </c>
+      <c r="I30" s="1">
+        <f>IF(MOD(A30,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
+        <f>IF(MOD(A30,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K30" s="1">
         <f t="shared" si="2"/>
-        <v>28.472492560065845</v>
-      </c>
-      <c r="J30" s="1">
+        <v>0.95105651629515364</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A31">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L30" s="1">
-        <f>SIN(2*PI()*B30/$D$4*$D$8)</f>
-        <v>0.95105651629515364</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A31">
+        <v>16</v>
+      </c>
+      <c r="B31" s="5">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B31">
-        <f>A31/$D$4*1000</f>
-        <v>16</v>
-      </c>
       <c r="C31" s="1">
-        <f>INDEX(J31:L31,1,$D$7)</f>
+        <f>INDEX(I31:K31,1,$D$7)</f>
         <v>0.90482705246601947</v>
       </c>
       <c r="D31" s="1">
-        <f>D30+$D$10*(C31-D30)</f>
+        <f t="shared" si="1"/>
         <v>0.93506995218757383</v>
       </c>
       <c r="E31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-46.229463829134176</v>
       </c>
       <c r="F31" s="1">
-        <f>(D31-D30)*1000</f>
+        <f t="shared" si="5"/>
         <v>-13.847962512597455</v>
       </c>
       <c r="G31" s="1">
+        <f t="shared" si="6"/>
+        <v>15.180575694163332</v>
+      </c>
+      <c r="I31" s="1">
+        <f>IF(MOD(A31,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="1">
+        <f>IF(MOD(A31,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K31" s="1">
         <f t="shared" si="2"/>
-        <v>15.180575694163332</v>
-      </c>
-      <c r="J31" s="1">
+        <v>0.90482705246601947</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A32">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L31" s="1">
-        <f>SIN(2*PI()*B31/$D$4*$D$8)</f>
-        <v>0.90482705246601947</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A32">
+        <v>17</v>
+      </c>
+      <c r="B32" s="5">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B32">
-        <f>A32/$D$4*1000</f>
-        <v>17</v>
-      </c>
       <c r="C32" s="1">
-        <f>INDEX(J32:L32,1,$D$7)</f>
+        <f>INDEX(I32:K32,1,$D$7)</f>
         <v>0.84432792550201519</v>
       </c>
       <c r="D32" s="1">
-        <f>D31+$D$10*(C32-D31)</f>
+        <f t="shared" si="1"/>
         <v>0.90656989298742952</v>
       </c>
       <c r="E32" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-60.499126964004276</v>
       </c>
       <c r="F32" s="1">
-        <f>(D32-D31)*1000</f>
+        <f t="shared" si="5"/>
         <v>-28.500059200144314</v>
       </c>
       <c r="G32" s="1">
+        <f t="shared" si="6"/>
+        <v>1.4614564959387124</v>
+      </c>
+      <c r="I32" s="1">
+        <f>IF(MOD(A32,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <f>IF(MOD(A32,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K32" s="1">
         <f t="shared" si="2"/>
-        <v>1.4614564959387124</v>
-      </c>
-      <c r="J32" s="1">
+        <v>0.84432792550201519</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A33">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K32" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L32" s="1">
-        <f>SIN(2*PI()*B32/$D$4*$D$8)</f>
-        <v>0.84432792550201519</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A33">
+        <v>18</v>
+      </c>
+      <c r="B33" s="5">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B33">
-        <f>A33/$D$4*1000</f>
-        <v>18</v>
-      </c>
       <c r="C33" s="1">
-        <f>INDEX(J33:L33,1,$D$7)</f>
+        <f>INDEX(I33:K33,1,$D$7)</f>
         <v>0.77051324277578925</v>
       </c>
       <c r="D33" s="1">
-        <f>D32+$D$10*(C33-D32)</f>
+        <f t="shared" si="1"/>
         <v>0.86383751497870476</v>
       </c>
       <c r="E33" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-73.814682726225939</v>
       </c>
       <c r="F33" s="1">
-        <f>(D33-D32)*1000</f>
+        <f t="shared" si="5"/>
         <v>-42.732378008724758</v>
       </c>
       <c r="G33" s="1">
+        <f t="shared" si="6"/>
+        <v>-12.418847324349896</v>
+      </c>
+      <c r="I33" s="1">
+        <f>IF(MOD(A33,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
+        <f>IF(MOD(A33,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K33" s="1">
         <f t="shared" si="2"/>
-        <v>-12.418847324349896</v>
-      </c>
-      <c r="J33" s="1">
+        <v>0.77051324277578925</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A34">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K33" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L33" s="1">
-        <f>SIN(2*PI()*B33/$D$4*$D$8)</f>
-        <v>0.77051324277578925</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A34">
+        <v>19</v>
+      </c>
+      <c r="B34" s="5">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B34">
-        <f>A34/$D$4*1000</f>
-        <v>19</v>
-      </c>
       <c r="C34" s="1">
-        <f>INDEX(J34:L34,1,$D$7)</f>
+        <f>INDEX(I34:K34,1,$D$7)</f>
         <v>0.68454710592868884</v>
       </c>
       <c r="D34" s="1">
-        <f>D33+$D$10*(C34-D33)</f>
+        <f t="shared" si="1"/>
         <v>0.80752637163549845</v>
       </c>
       <c r="E34" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-85.966136847100415</v>
       </c>
       <c r="F34" s="1">
-        <f>(D34-D33)*1000</f>
+        <f t="shared" si="5"/>
         <v>-56.311143343206304</v>
       </c>
       <c r="G34" s="1">
+        <f t="shared" si="6"/>
+        <v>-26.20444459012873</v>
+      </c>
+      <c r="I34" s="1">
+        <f>IF(MOD(A34,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="1">
+        <f>IF(MOD(A34,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K34" s="1">
         <f t="shared" si="2"/>
-        <v>-26.20444459012873</v>
-      </c>
-      <c r="J34" s="1">
+        <v>0.68454710592868884</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A35">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L34" s="1">
-        <f>SIN(2*PI()*B34/$D$4*$D$8)</f>
-        <v>0.68454710592868884</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A35">
+        <v>20</v>
+      </c>
+      <c r="B35" s="5">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B35">
-        <f>A35/$D$4*1000</f>
-        <v>20</v>
-      </c>
       <c r="C35" s="1">
-        <f>INDEX(J35:L35,1,$D$7)</f>
+        <f>INDEX(I35:K35,1,$D$7)</f>
         <v>0.58778525229247325</v>
       </c>
       <c r="D35" s="1">
-        <f>D34+$D$10*(C35-D34)</f>
+        <f t="shared" si="1"/>
         <v>0.73851055681703925</v>
       </c>
       <c r="E35" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-96.761853636215591</v>
       </c>
       <c r="F35" s="1">
-        <f>(D35-D34)*1000</f>
+        <f t="shared" si="5"/>
         <v>-69.015814818459205</v>
       </c>
       <c r="G35" s="1">
+        <f t="shared" si="6"/>
+        <v>-39.65054702483328</v>
+      </c>
+      <c r="I35" s="1">
+        <f>IF(MOD(A35,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <f>IF(MOD(A35,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K35" s="1">
         <f t="shared" si="2"/>
-        <v>-39.65054702483328</v>
-      </c>
-      <c r="J35" s="1">
+        <v>0.58778525229247325</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A36">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K35" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L35" s="1">
-        <f>SIN(2*PI()*B35/$D$4*$D$8)</f>
-        <v>0.58778525229247325</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A36">
+        <v>21</v>
+      </c>
+      <c r="B36" s="5">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B36">
-        <f>A36/$D$4*1000</f>
-        <v>21</v>
-      </c>
       <c r="C36" s="1">
-        <f>INDEX(J36:L36,1,$D$7)</f>
+        <f>INDEX(I36:K36,1,$D$7)</f>
         <v>0.48175367410171521</v>
       </c>
       <c r="D36" s="1">
-        <f>D35+$D$10*(C36-D35)</f>
+        <f t="shared" si="1"/>
         <v>0.65786891121231494</v>
       </c>
       <c r="E36" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-106.03157819075804</v>
       </c>
       <c r="F36" s="1">
-        <f>(D36-D35)*1000</f>
+        <f t="shared" si="5"/>
         <v>-80.641645604724317</v>
       </c>
       <c r="G36" s="1">
+        <f t="shared" si="6"/>
+        <v>-52.524942482784525</v>
+      </c>
+      <c r="I36" s="1">
+        <f>IF(MOD(A36,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="1">
+        <f>IF(MOD(A36,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K36" s="1">
         <f t="shared" si="2"/>
-        <v>-52.524942482784525</v>
-      </c>
-      <c r="J36" s="1">
+        <v>0.48175367410171521</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A37">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K36" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L36" s="1">
-        <f>SIN(2*PI()*B36/$D$4*$D$8)</f>
-        <v>0.48175367410171521</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A37">
+        <v>22</v>
+      </c>
+      <c r="B37" s="5">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B37">
-        <f>A37/$D$4*1000</f>
-        <v>22</v>
-      </c>
       <c r="C37" s="1">
-        <f>INDEX(J37:L37,1,$D$7)</f>
+        <f>INDEX(I37:K37,1,$D$7)</f>
         <v>0.36812455268467853</v>
       </c>
       <c r="D37" s="1">
-        <f>D36+$D$10*(C37-D36)</f>
+        <f t="shared" si="1"/>
         <v>0.56686663065316056</v>
       </c>
       <c r="E37" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-113.62912141703669</v>
       </c>
       <c r="F37" s="1">
-        <f>(D37-D36)*1000</f>
+        <f t="shared" si="5"/>
         <v>-91.002280559154386</v>
       </c>
       <c r="G37" s="1">
+        <f t="shared" si="6"/>
+        <v>-64.609821486429595</v>
+      </c>
+      <c r="I37" s="1">
+        <f>IF(MOD(A37,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="1">
+        <f>IF(MOD(A37,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K37" s="1">
         <f t="shared" si="2"/>
-        <v>-64.609821486429595</v>
-      </c>
-      <c r="J37" s="1">
+        <v>0.36812455268467853</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A38">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K37" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L37" s="1">
-        <f>SIN(2*PI()*B37/$D$4*$D$8)</f>
-        <v>0.36812455268467853</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A38">
+        <v>23</v>
+      </c>
+      <c r="B38" s="5">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B38">
-        <f>A38/$D$4*1000</f>
-        <v>23</v>
-      </c>
       <c r="C38" s="1">
-        <f>INDEX(J38:L38,1,$D$7)</f>
+        <f>INDEX(I38:K38,1,$D$7)</f>
         <v>0.24868988716485482</v>
       </c>
       <c r="D38" s="1">
-        <f>D37+$D$10*(C38-D37)</f>
+        <f t="shared" si="1"/>
         <v>0.46693436820823314</v>
       </c>
       <c r="E38" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-119.43466551982371</v>
       </c>
       <c r="F38" s="1">
-        <f>(D38-D37)*1000</f>
+        <f t="shared" si="5"/>
         <v>-99.932262444927417</v>
       </c>
       <c r="G38" s="1">
+        <f t="shared" si="6"/>
+        <v>-75.703817236592883</v>
+      </c>
+      <c r="I38" s="1">
+        <f>IF(MOD(A38,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <f>IF(MOD(A38,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K38" s="1">
         <f t="shared" si="2"/>
-        <v>-75.703817236592883</v>
-      </c>
-      <c r="J38" s="1">
+        <v>0.24868988716485482</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A39">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K38" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L38" s="1">
-        <f>SIN(2*PI()*B38/$D$4*$D$8)</f>
-        <v>0.24868988716485482</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A39">
+        <v>24</v>
+      </c>
+      <c r="B39" s="5">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B39">
-        <f>A39/$D$4*1000</f>
-        <v>24</v>
-      </c>
       <c r="C39" s="1">
-        <f>INDEX(J39:L39,1,$D$7)</f>
+        <f>INDEX(I39:K39,1,$D$7)</f>
         <v>0.12533323356430454</v>
       </c>
       <c r="D39" s="1">
-        <f>D38+$D$10*(C39-D38)</f>
+        <f t="shared" si="1"/>
         <v>0.35964502372483681</v>
       </c>
       <c r="E39" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-123.35665360055029</v>
       </c>
       <c r="F39" s="1">
-        <f>(D39-D38)*1000</f>
+        <f t="shared" si="5"/>
         <v>-107.28934448339633</v>
       </c>
       <c r="G39" s="1">
+        <f t="shared" si="6"/>
+        <v>-85.624131222096281</v>
+      </c>
+      <c r="I39" s="1">
+        <f>IF(MOD(A39,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="1">
+        <f>IF(MOD(A39,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K39" s="1">
         <f t="shared" si="2"/>
-        <v>-85.624131222096281</v>
-      </c>
-      <c r="J39" s="1">
+        <v>0.12533323356430454</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A40">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K39" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L39" s="1">
-        <f>SIN(2*PI()*B39/$D$4*$D$8)</f>
-        <v>0.12533323356430454</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A40">
+        <v>25</v>
+      </c>
+      <c r="B40" s="5">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B40">
-        <f>A40/$D$4*1000</f>
-        <v>25</v>
-      </c>
       <c r="C40" s="1">
-        <f>INDEX(J40:L40,1,$D$7)</f>
+        <f>INDEX(I40:K40,1,$D$7)</f>
         <v>1.22514845490862E-16</v>
       </c>
       <c r="D40" s="1">
-        <f>D39+$D$10*(C40-D39)</f>
+        <f t="shared" si="1"/>
         <v>0.24668849364078474</v>
       </c>
       <c r="E40" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-125.33323356430442</v>
       </c>
       <c r="F40" s="1">
-        <f>(D40-D39)*1000</f>
+        <f t="shared" si="5"/>
         <v>-112.95653008405208</v>
       </c>
       <c r="G40" s="1">
+        <f t="shared" si="6"/>
+        <v>-94.20863185648281</v>
+      </c>
+      <c r="I40" s="1">
+        <f>IF(MOD(A40,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="1">
+        <f>IF(MOD(A40,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
         <f t="shared" si="2"/>
-        <v>-94.20863185648281</v>
-      </c>
-      <c r="J40" s="1">
+        <v>1.22514845490862E-16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A41">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K40" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L40" s="1">
-        <f>SIN(2*PI()*B40/$D$4*$D$8)</f>
-        <v>1.22514845490862E-16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A41">
+        <v>26</v>
+      </c>
+      <c r="B41" s="5">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B41">
-        <f>A41/$D$4*1000</f>
-        <v>26</v>
-      </c>
       <c r="C41" s="1">
-        <f>INDEX(J41:L41,1,$D$7)</f>
+        <f>INDEX(I41:K41,1,$D$7)</f>
         <v>-0.12533323356430473</v>
       </c>
       <c r="D41" s="1">
-        <f>D40+$D$10*(C41-D40)</f>
+        <f t="shared" si="1"/>
         <v>0.12984471533477981</v>
       </c>
       <c r="E41" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-125.33323356430485</v>
       </c>
       <c r="F41" s="1">
-        <f>(D41-D40)*1000</f>
+        <f t="shared" si="5"/>
         <v>-116.84377830600492</v>
       </c>
       <c r="G41" s="1">
+        <f t="shared" si="6"/>
+        <v>-101.31782962711166</v>
+      </c>
+      <c r="I41" s="1">
+        <f>IF(MOD(A41,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <f>IF(MOD(A41,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
         <f t="shared" si="2"/>
-        <v>-101.31782962711166</v>
-      </c>
-      <c r="J41" s="1">
+        <v>-0.12533323356430473</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A42">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K41" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L41" s="1">
-        <f>SIN(2*PI()*B41/$D$4*$D$8)</f>
-        <v>-0.12533323356430473</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A42">
+        <v>27</v>
+      </c>
+      <c r="B42" s="5">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B42">
-        <f>A42/$D$4*1000</f>
-        <v>27</v>
-      </c>
       <c r="C42" s="1">
-        <f>INDEX(J42:L42,1,$D$7)</f>
+        <f>INDEX(I42:K42,1,$D$7)</f>
         <v>-0.24868988716485457</v>
       </c>
       <c r="D42" s="1">
-        <f>D41+$D$10*(C42-D41)</f>
+        <f t="shared" si="1"/>
         <v>1.095538726272334E-2</v>
       </c>
       <c r="E42" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-123.35665360054985</v>
       </c>
       <c r="F42" s="1">
-        <f>(D42-D41)*1000</f>
+        <f t="shared" si="5"/>
         <v>-118.88932807205647</v>
       </c>
       <c r="G42" s="1">
+        <f t="shared" si="6"/>
+        <v>-106.8366477999911</v>
+      </c>
+      <c r="I42" s="1">
+        <f>IF(MOD(A42,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <f>IF(MOD(A42,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
         <f t="shared" si="2"/>
-        <v>-106.8366477999911</v>
-      </c>
-      <c r="J42" s="1">
+        <v>-0.24868988716485457</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A43">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K42" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L42" s="1">
-        <f>SIN(2*PI()*B42/$D$4*$D$8)</f>
-        <v>-0.24868988716485457</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A43">
+        <v>28</v>
+      </c>
+      <c r="B43" s="5">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B43">
-        <f>A43/$D$4*1000</f>
-        <v>28</v>
-      </c>
       <c r="C43" s="1">
-        <f>INDEX(J43:L43,1,$D$7)</f>
+        <f>INDEX(I43:K43,1,$D$7)</f>
         <v>-0.36812455268467748</v>
       </c>
       <c r="D43" s="1">
-        <f>D42+$D$10*(C43-D42)</f>
+        <f t="shared" si="1"/>
         <v>-0.10810521921376261</v>
       </c>
       <c r="E43" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-119.4346655198229</v>
       </c>
       <c r="F43" s="1">
-        <f>(D43-D42)*1000</f>
+        <f t="shared" si="5"/>
         <v>-119.06060647648594</v>
       </c>
       <c r="G43" s="1">
+        <f t="shared" si="6"/>
+        <v>-110.67592226481486</v>
+      </c>
+      <c r="I43" s="1">
+        <f>IF(MOD(A43,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <f>IF(MOD(A43,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
         <f t="shared" si="2"/>
-        <v>-110.67592226481486</v>
-      </c>
-      <c r="J43" s="1">
+        <v>-0.36812455268467748</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A44">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K43" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L43" s="1">
-        <f>SIN(2*PI()*B43/$D$4*$D$8)</f>
-        <v>-0.36812455268467748</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A44">
+        <v>29</v>
+      </c>
+      <c r="B44" s="5">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B44">
-        <f>A44/$D$4*1000</f>
-        <v>29</v>
-      </c>
       <c r="C44" s="1">
-        <f>INDEX(J44:L44,1,$D$7)</f>
+        <f>INDEX(I44:K44,1,$D$7)</f>
         <v>-0.48175367410171538</v>
       </c>
       <c r="D44" s="1">
-        <f>D43+$D$10*(C44-D43)</f>
+        <f t="shared" si="1"/>
         <v>-0.2254599166270162</v>
       </c>
       <c r="E44" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-113.62912141703791</v>
       </c>
       <c r="F44" s="1">
-        <f>(D44-D43)*1000</f>
+        <f t="shared" si="5"/>
         <v>-117.35469741325359</v>
       </c>
       <c r="G44" s="1">
+        <f t="shared" si="6"/>
+        <v>-112.77357749764921</v>
+      </c>
+      <c r="I44" s="1">
+        <f>IF(MOD(A44,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <f>IF(MOD(A44,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
         <f t="shared" si="2"/>
-        <v>-112.77357749764921</v>
-      </c>
-      <c r="J44" s="1">
+        <v>-0.48175367410171538</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A45">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K44" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L44" s="1">
-        <f>SIN(2*PI()*B44/$D$4*$D$8)</f>
-        <v>-0.48175367410171538</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A45">
+        <v>30</v>
+      </c>
+      <c r="B45" s="5">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B45">
-        <f>A45/$D$4*1000</f>
-        <v>30</v>
-      </c>
       <c r="C45" s="1">
-        <f>INDEX(J45:L45,1,$D$7)</f>
+        <f>INDEX(I45:K45,1,$D$7)</f>
         <v>-0.58778525229247303</v>
       </c>
       <c r="D45" s="1">
-        <f>D44+$D$10*(C45-D44)</f>
+        <f t="shared" si="1"/>
         <v>-0.33925827327999902</v>
       </c>
       <c r="E45" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-106.03157819075764</v>
       </c>
       <c r="F45" s="1">
-        <f>(D45-D44)*1000</f>
+        <f t="shared" si="5"/>
         <v>-113.79835665298282</v>
       </c>
       <c r="G45" s="1">
+        <f t="shared" si="6"/>
+        <v>-113.0954379151522</v>
+      </c>
+      <c r="I45" s="1">
+        <f>IF(MOD(A45,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="1">
+        <f>IF(MOD(A45,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
         <f t="shared" si="2"/>
-        <v>-113.0954379151522</v>
-      </c>
-      <c r="J45" s="1">
+        <v>-0.58778525229247303</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A46">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K45" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L45" s="1">
-        <f>SIN(2*PI()*B45/$D$4*$D$8)</f>
-        <v>-0.58778525229247303</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A46">
+        <v>31</v>
+      </c>
+      <c r="B46" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B46">
-        <f>A46/$D$4*1000</f>
-        <v>31</v>
-      </c>
       <c r="C46" s="1">
-        <f>INDEX(J46:L46,1,$D$7)</f>
+        <f>INDEX(I46:K46,1,$D$7)</f>
         <v>-0.68454710592868839</v>
       </c>
       <c r="D46" s="1">
-        <f>D45+$D$10*(C46-D45)</f>
+        <f t="shared" si="1"/>
         <v>-0.44770584196541952</v>
       </c>
       <c r="E46" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-96.761853636215363</v>
       </c>
       <c r="F46" s="1">
-        <f>(D46-D45)*1000</f>
+        <f t="shared" si="5"/>
         <v>-108.44756868542049</v>
       </c>
       <c r="G46" s="1">
+        <f t="shared" si="6"/>
+        <v>-111.63564521445683</v>
+      </c>
+      <c r="I46" s="1">
+        <f>IF(MOD(A46,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <f>IF(MOD(A46,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K46" s="1">
         <f t="shared" si="2"/>
-        <v>-111.63564521445683</v>
-      </c>
-      <c r="J46" s="1">
+        <v>-0.68454710592868839</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A47">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K46" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L46" s="1">
-        <f>SIN(2*PI()*B46/$D$4*$D$8)</f>
-        <v>-0.68454710592868839</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A47">
+        <v>32</v>
+      </c>
+      <c r="B47" s="5">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B47">
-        <f>A47/$D$4*1000</f>
-        <v>32</v>
-      </c>
       <c r="C47" s="1">
-        <f>INDEX(J47:L47,1,$D$7)</f>
+        <f>INDEX(I47:K47,1,$D$7)</f>
         <v>-0.77051324277578936</v>
       </c>
       <c r="D47" s="1">
-        <f>D46+$D$10*(C47-D46)</f>
+        <f t="shared" ref="D47:D78" si="7">D46+$D$10*(C47-D46)</f>
         <v>-0.54909249123236192</v>
       </c>
       <c r="E47" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-85.966136847100969</v>
       </c>
       <c r="F47" s="1">
-        <f>(D47-D46)*1000</f>
+        <f t="shared" si="5"/>
         <v>-101.38664926694241</v>
       </c>
       <c r="G47" s="1">
+        <f t="shared" si="6"/>
+        <v>-108.41666276591199</v>
+      </c>
+      <c r="I47" s="1">
+        <f>IF(MOD(A47,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <f>IF(MOD(A47,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
         <f t="shared" si="2"/>
-        <v>-108.41666276591199</v>
-      </c>
-      <c r="J47" s="1">
+        <v>-0.77051324277578936</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A48">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K47" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L47" s="1">
-        <f>SIN(2*PI()*B47/$D$4*$D$8)</f>
-        <v>-0.77051324277578936</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A48">
+        <v>33</v>
+      </c>
+      <c r="B48" s="5">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B48">
-        <f>A48/$D$4*1000</f>
-        <v>33</v>
-      </c>
       <c r="C48" s="1">
-        <f>INDEX(J48:L48,1,$D$7)</f>
+        <f>INDEX(I48:K48,1,$D$7)</f>
         <v>-0.8443279255020153</v>
       </c>
       <c r="D48" s="1">
-        <f>D47+$D$10*(C48-D47)</f>
+        <f t="shared" si="7"/>
         <v>-0.64181939696726042</v>
       </c>
       <c r="E48" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-73.814682726225939</v>
       </c>
       <c r="F48" s="1">
-        <f>(D48-D47)*1000</f>
+        <f t="shared" ref="F48:F79" si="8">(D48-D47)*1000</f>
         <v>-92.726905734898509</v>
       </c>
       <c r="G48" s="1">
+        <f t="shared" si="6"/>
+        <v>-103.48885786059209</v>
+      </c>
+      <c r="I48" s="1">
+        <f>IF(MOD(A48,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
+        <f>IF(MOD(A48,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K48" s="1">
         <f t="shared" si="2"/>
-        <v>-103.48885786059209</v>
-      </c>
-      <c r="J48" s="1">
+        <v>-0.8443279255020153</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A49">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K48" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L48" s="1">
-        <f>SIN(2*PI()*B48/$D$4*$D$8)</f>
-        <v>-0.8443279255020153</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A49">
+        <v>34</v>
+      </c>
+      <c r="B49" s="5">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B49">
-        <f>A49/$D$4*1000</f>
-        <v>34</v>
-      </c>
       <c r="C49" s="1">
-        <f>INDEX(J49:L49,1,$D$7)</f>
+        <f>INDEX(I49:K49,1,$D$7)</f>
         <v>-0.90482705246601935</v>
       </c>
       <c r="D49" s="1">
-        <f>D48+$D$10*(C49-D48)</f>
+        <f t="shared" si="7"/>
         <v>-0.72442427174904356</v>
       </c>
       <c r="E49" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-60.499126964004056</v>
       </c>
       <c r="F49" s="1">
-        <f>(D49-D48)*1000</f>
+        <f t="shared" si="8"/>
         <v>-82.604874781783138</v>
       </c>
       <c r="G49" s="1">
+        <f t="shared" si="6"/>
+        <v>-96.929661688532249</v>
+      </c>
+      <c r="I49" s="1">
+        <f>IF(MOD(A49,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="1">
+        <f>IF(MOD(A49,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="1">
         <f t="shared" si="2"/>
-        <v>-96.929661688532249</v>
-      </c>
-      <c r="J49" s="1">
+        <v>-0.90482705246601935</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A50">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K49" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L49" s="1">
-        <f>SIN(2*PI()*B49/$D$4*$D$8)</f>
-        <v>-0.90482705246601935</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A50">
+        <v>35</v>
+      </c>
+      <c r="B50" s="5">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B50">
-        <f>A50/$D$4*1000</f>
-        <v>35</v>
-      </c>
       <c r="C50" s="1">
-        <f>INDEX(J50:L50,1,$D$7)</f>
+        <f>INDEX(I50:K50,1,$D$7)</f>
         <v>-0.95105651629515353</v>
       </c>
       <c r="D50" s="1">
-        <f>D49+$D$10*(C50-D49)</f>
+        <f t="shared" si="7"/>
         <v>-0.7956044362455641</v>
       </c>
       <c r="E50" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-46.229463829134176</v>
       </c>
       <c r="F50" s="1">
-        <f>(D50-D49)*1000</f>
+        <f t="shared" si="8"/>
         <v>-71.180164496520533</v>
       </c>
       <c r="G50" s="1">
+        <f t="shared" si="6"/>
+        <v>-88.842315382180942</v>
+      </c>
+      <c r="I50" s="1">
+        <f>IF(MOD(A50,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
+        <f>IF(MOD(A50,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
         <f t="shared" si="2"/>
-        <v>-88.842315382180942</v>
-      </c>
-      <c r="J50" s="1">
+        <v>-0.95105651629515353</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A51">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K50" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L50" s="1">
-        <f>SIN(2*PI()*B50/$D$4*$D$8)</f>
-        <v>-0.95105651629515353</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A51">
+        <v>36</v>
+      </c>
+      <c r="B51" s="5">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B51">
-        <f>A51/$D$4*1000</f>
-        <v>36</v>
-      </c>
       <c r="C51" s="1">
-        <f>INDEX(J51:L51,1,$D$7)</f>
+        <f>INDEX(I51:K51,1,$D$7)</f>
         <v>-0.98228725072868872</v>
       </c>
       <c r="D51" s="1">
-        <f>D50+$D$10*(C51-D50)</f>
+        <f t="shared" si="7"/>
         <v>-0.85423737027573776</v>
       </c>
       <c r="E51" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-31.23073443353519</v>
       </c>
       <c r="F51" s="1">
-        <f>(D51-D50)*1000</f>
+        <f t="shared" si="8"/>
         <v>-58.632934030173665</v>
       </c>
       <c r="G51" s="1">
+        <f t="shared" si="6"/>
+        <v>-79.354218318673716</v>
+      </c>
+      <c r="I51" s="1">
+        <f>IF(MOD(A51,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="1">
+        <f>IF(MOD(A51,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
         <f t="shared" si="2"/>
-        <v>-79.354218318673716</v>
-      </c>
-      <c r="J51" s="1">
+        <v>-0.98228725072868872</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A52">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K51" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L51" s="1">
-        <f>SIN(2*PI()*B51/$D$4*$D$8)</f>
-        <v>-0.98228725072868872</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A52">
+        <v>37</v>
+      </c>
+      <c r="B52" s="5">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B52">
-        <f>A52/$D$4*1000</f>
-        <v>37</v>
-      </c>
       <c r="C52" s="1">
-        <f>INDEX(J52:L52,1,$D$7)</f>
+        <f>INDEX(I52:K52,1,$D$7)</f>
         <v>-0.99802672842827156</v>
       </c>
       <c r="D52" s="1">
-        <f>D51+$D$10*(C52-D51)</f>
+        <f t="shared" si="7"/>
         <v>-0.89939842044600204</v>
       </c>
       <c r="E52" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-15.739477699582839</v>
       </c>
       <c r="F52" s="1">
-        <f>(D52-D51)*1000</f>
+        <f t="shared" si="8"/>
         <v>-45.161050170264282</v>
       </c>
       <c r="G52" s="1">
+        <f t="shared" si="6"/>
+        <v>-68.614902126772421</v>
+      </c>
+      <c r="I52" s="1">
+        <f>IF(MOD(A52,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="1">
+        <f>IF(MOD(A52,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
         <f t="shared" si="2"/>
-        <v>-68.614902126772421</v>
-      </c>
-      <c r="J52" s="1">
+        <v>-0.99802672842827156</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A53">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K52" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L52" s="1">
-        <f>SIN(2*PI()*B52/$D$4*$D$8)</f>
-        <v>-0.99802672842827156</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A53">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B53">
-        <f>A53/$D$4*1000</f>
-        <v>38</v>
-      </c>
       <c r="C53" s="1">
-        <f>INDEX(J53:L53,1,$D$7)</f>
+        <f>INDEX(I53:K53,1,$D$7)</f>
         <v>-0.99802672842827156</v>
       </c>
       <c r="D53" s="1">
-        <f>D52+$D$10*(C53-D52)</f>
+        <f t="shared" si="7"/>
         <v>-0.93037538579465118</v>
       </c>
       <c r="E53" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F53" s="1">
-        <f>(D53-D52)*1000</f>
+        <f t="shared" si="8"/>
         <v>-30.976965348649131</v>
       </c>
       <c r="G53" s="1">
+        <f t="shared" si="6"/>
+        <v>-56.79366046479268</v>
+      </c>
+      <c r="I53" s="1">
+        <f>IF(MOD(A53,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
+        <f>IF(MOD(A53,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="1">
         <f t="shared" si="2"/>
-        <v>-56.79366046479268</v>
-      </c>
-      <c r="J53" s="1">
+        <v>-0.99802672842827156</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A54">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K53" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L53" s="1">
-        <f>SIN(2*PI()*B53/$D$4*$D$8)</f>
-        <v>-0.99802672842827156</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A54">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B54">
-        <f>A54/$D$4*1000</f>
-        <v>39</v>
-      </c>
       <c r="C54" s="1">
-        <f>INDEX(J54:L54,1,$D$7)</f>
+        <f>INDEX(I54:K54,1,$D$7)</f>
         <v>-0.98228725072868872</v>
       </c>
       <c r="D54" s="1">
-        <f>D53+$D$10*(C54-D53)</f>
+        <f t="shared" si="7"/>
         <v>-0.94667975189545184</v>
       </c>
       <c r="E54" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>15.739477699582839</v>
       </c>
       <c r="F54" s="1">
-        <f>(D54-D53)*1000</f>
+        <f t="shared" si="8"/>
         <v>-16.30436610080066</v>
       </c>
       <c r="G54" s="1">
+        <f t="shared" si="6"/>
+        <v>-44.076870588096099</v>
+      </c>
+      <c r="I54" s="1">
+        <f>IF(MOD(A54,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="1">
+        <f>IF(MOD(A54,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K54" s="1">
         <f t="shared" si="2"/>
-        <v>-44.076870588096099</v>
-      </c>
-      <c r="J54" s="1">
+        <v>-0.98228725072868872</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A55">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K54" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L54" s="1">
-        <f>SIN(2*PI()*B54/$D$4*$D$8)</f>
-        <v>-0.98228725072868872</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A55">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B55">
-        <f>A55/$D$4*1000</f>
-        <v>40</v>
-      </c>
       <c r="C55" s="1">
-        <f>INDEX(J55:L55,1,$D$7)</f>
+        <f>INDEX(I55:K55,1,$D$7)</f>
         <v>-0.95105651629515364</v>
       </c>
       <c r="D55" s="1">
-        <f>D54+$D$10*(C55-D54)</f>
+        <f t="shared" si="7"/>
         <v>-0.94805439657832657</v>
       </c>
       <c r="E55" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>31.23073443353508</v>
       </c>
       <c r="F55" s="1">
-        <f>(D55-D54)*1000</f>
+        <f t="shared" si="8"/>
         <v>-1.3746446828747372</v>
       </c>
       <c r="G55" s="1">
+        <f t="shared" si="6"/>
+        <v>-30.665047965994241</v>
+      </c>
+      <c r="I55" s="1">
+        <f>IF(MOD(A55,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="1">
+        <f>IF(MOD(A55,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K55" s="1">
         <f t="shared" si="2"/>
-        <v>-30.665047965994241</v>
-      </c>
-      <c r="J55" s="1">
+        <v>-0.95105651629515364</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A56">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K55" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L55" s="1">
-        <f>SIN(2*PI()*B55/$D$4*$D$8)</f>
-        <v>-0.95105651629515364</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A56">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B56">
-        <f>A56/$D$4*1000</f>
-        <v>41</v>
-      </c>
       <c r="C56" s="1">
-        <f>INDEX(J56:L56,1,$D$7)</f>
+        <f>INDEX(I56:K56,1,$D$7)</f>
         <v>-0.90482705246601991</v>
       </c>
       <c r="D56" s="1">
-        <f>D55+$D$10*(C56-D55)</f>
+        <f t="shared" si="7"/>
         <v>-0.9344776459671148</v>
       </c>
       <c r="E56" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>46.229463829133735</v>
       </c>
       <c r="F56" s="1">
-        <f>(D56-D55)*1000</f>
+        <f t="shared" si="8"/>
         <v>13.576750611211775</v>
       </c>
       <c r="G56" s="1">
+        <f t="shared" si="6"/>
+        <v>-16.769679693688495</v>
+      </c>
+      <c r="I56" s="1">
+        <f>IF(MOD(A56,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="1">
+        <f>IF(MOD(A56,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
         <f t="shared" si="2"/>
-        <v>-16.769679693688495</v>
-      </c>
-      <c r="J56" s="1">
+        <v>-0.90482705246601991</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A57">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K56" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L56" s="1">
-        <f>SIN(2*PI()*B56/$D$4*$D$8)</f>
-        <v>-0.90482705246601991</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A57">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B57">
-        <f>A57/$D$4*1000</f>
-        <v>42</v>
-      </c>
       <c r="C57" s="1">
-        <f>INDEX(J57:L57,1,$D$7)</f>
+        <f>INDEX(I57:K57,1,$D$7)</f>
         <v>-0.84432792550201496</v>
       </c>
       <c r="D57" s="1">
-        <f>D56+$D$10*(C57-D56)</f>
+        <f t="shared" si="7"/>
         <v>-0.90616361702179593</v>
       </c>
       <c r="E57" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>60.499126964004944</v>
       </c>
       <c r="F57" s="1">
-        <f>(D57-D56)*1000</f>
+        <f t="shared" si="8"/>
         <v>28.314028945318871</v>
       </c>
       <c r="G57" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.609886132693946</v>
+      </c>
+      <c r="I57" s="1">
+        <f>IF(MOD(A57,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="1">
+        <f>IF(MOD(A57,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
         <f t="shared" si="2"/>
-        <v>-2.609886132693946</v>
-      </c>
-      <c r="J57" s="1">
+        <v>-0.84432792550201496</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A58">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K57" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L57" s="1">
-        <f>SIN(2*PI()*B57/$D$4*$D$8)</f>
-        <v>-0.84432792550201496</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A58">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B58">
-        <f>A58/$D$4*1000</f>
-        <v>43</v>
-      </c>
       <c r="C58" s="1">
-        <f>INDEX(J58:L58,1,$D$7)</f>
+        <f>INDEX(I58:K58,1,$D$7)</f>
         <v>-0.77051324277578903</v>
       </c>
       <c r="D58" s="1">
-        <f>D57+$D$10*(C58-D57)</f>
+        <f t="shared" si="7"/>
         <v>-0.86355884128839033</v>
       </c>
       <c r="E58" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>73.814682726225939</v>
       </c>
       <c r="F58" s="1">
-        <f>(D58-D57)*1000</f>
+        <f t="shared" si="8"/>
         <v>42.604775733405596</v>
       </c>
       <c r="G58" s="1">
+        <f t="shared" si="6"/>
+        <v>11.591036934229642</v>
+      </c>
+      <c r="I58" s="1">
+        <f>IF(MOD(A58,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <f>IF(MOD(A58,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
         <f t="shared" si="2"/>
-        <v>11.591036934229642</v>
-      </c>
-      <c r="J58" s="1">
+        <v>-0.77051324277578903</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A59">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L58" s="1">
-        <f>SIN(2*PI()*B58/$D$4*$D$8)</f>
-        <v>-0.77051324277578903</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A59">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B59">
-        <f>A59/$D$4*1000</f>
-        <v>44</v>
-      </c>
       <c r="C59" s="1">
-        <f>INDEX(J59:L59,1,$D$7)</f>
+        <f>INDEX(I59:K59,1,$D$7)</f>
         <v>-0.68454710592868961</v>
       </c>
       <c r="D59" s="1">
-        <f>D58+$D$10*(C59-D58)</f>
+        <f t="shared" si="7"/>
         <v>-0.80733522317424933</v>
       </c>
       <c r="E59" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>85.96613684709942</v>
       </c>
       <c r="F59" s="1">
-        <f>(D59-D58)*1000</f>
+        <f t="shared" si="8"/>
         <v>56.223618114141004</v>
       </c>
       <c r="G59" s="1">
+        <f t="shared" si="6"/>
+        <v>25.609141359983695</v>
+      </c>
+      <c r="I59" s="1">
+        <f>IF(MOD(A59,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J59" s="1">
+        <f>IF(MOD(A59,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K59" s="1">
         <f t="shared" si="2"/>
-        <v>25.609141359983695</v>
-      </c>
-      <c r="J59" s="1">
+        <v>-0.68454710592868961</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A60">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K59" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L59" s="1">
-        <f>SIN(2*PI()*B59/$D$4*$D$8)</f>
-        <v>-0.68454710592868961</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A60">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B60">
-        <f>A60/$D$4*1000</f>
-        <v>45</v>
-      </c>
       <c r="C60" s="1">
-        <f>INDEX(J60:L60,1,$D$7)</f>
+        <f>INDEX(I60:K60,1,$D$7)</f>
         <v>-0.58778525229247336</v>
       </c>
       <c r="D60" s="1">
-        <f>D59+$D$10*(C60-D59)</f>
+        <f t="shared" si="7"/>
         <v>-0.73837944385048426</v>
       </c>
       <c r="E60" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>96.761853636216259</v>
       </c>
       <c r="F60" s="1">
-        <f>(D60-D59)*1000</f>
+        <f t="shared" si="8"/>
         <v>68.955779323765071</v>
       </c>
       <c r="G60" s="1">
+        <f t="shared" si="6"/>
+        <v>39.223359525683989</v>
+      </c>
+      <c r="I60" s="1">
+        <f>IF(MOD(A60,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J60" s="1">
+        <f>IF(MOD(A60,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="1">
         <f t="shared" si="2"/>
-        <v>39.223359525683989</v>
-      </c>
-      <c r="J60" s="1">
+        <v>-0.58778525229247336</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A61">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K60" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L60" s="1">
-        <f>SIN(2*PI()*B60/$D$4*$D$8)</f>
-        <v>-0.58778525229247336</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A61">
+        <v>46</v>
+      </c>
+      <c r="B61" s="5">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B61">
-        <f>A61/$D$4*1000</f>
-        <v>46</v>
-      </c>
       <c r="C61" s="1">
-        <f>INDEX(J61:L61,1,$D$7)</f>
+        <f>INDEX(I61:K61,1,$D$7)</f>
         <v>-0.48175367410171532</v>
       </c>
       <c r="D61" s="1">
-        <f>D60+$D$10*(C61-D60)</f>
+        <f t="shared" si="7"/>
         <v>-0.65777897792231355</v>
       </c>
       <c r="E61" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>106.03157819075804</v>
       </c>
       <c r="F61" s="1">
-        <f>(D61-D60)*1000</f>
+        <f t="shared" si="8"/>
         <v>80.600465928170721</v>
       </c>
       <c r="G61" s="1">
+        <f t="shared" si="6"/>
+        <v>52.218991484488562</v>
+      </c>
+      <c r="I61" s="1">
+        <f>IF(MOD(A61,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J61" s="1">
+        <f>IF(MOD(A61,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K61" s="1">
         <f t="shared" si="2"/>
-        <v>52.218991484488562</v>
-      </c>
-      <c r="J61" s="1">
+        <v>-0.48175367410171532</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A62">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K61" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L61" s="1">
-        <f>SIN(2*PI()*B61/$D$4*$D$8)</f>
-        <v>-0.48175367410171532</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A62">
+        <v>47</v>
+      </c>
+      <c r="B62" s="5">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B62">
-        <f>A62/$D$4*1000</f>
-        <v>47</v>
-      </c>
       <c r="C62" s="1">
-        <f>INDEX(J62:L62,1,$D$7)</f>
+        <f>INDEX(I62:K62,1,$D$7)</f>
         <v>-0.36812455268467786</v>
       </c>
       <c r="D62" s="1">
-        <f>D61+$D$10*(C62-D61)</f>
+        <f t="shared" si="7"/>
         <v>-0.566804943416093</v>
       </c>
       <c r="E62" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>113.62912141703745</v>
       </c>
       <c r="F62" s="1">
-        <f>(D62-D61)*1000</f>
+        <f t="shared" si="8"/>
         <v>90.974034506220548</v>
       </c>
       <c r="G62" s="1">
+        <f t="shared" si="6"/>
+        <v>64.391091455882346</v>
+      </c>
+      <c r="I62" s="1">
+        <f>IF(MOD(A62,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J62" s="1">
+        <f>IF(MOD(A62,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K62" s="1">
         <f t="shared" si="2"/>
-        <v>64.391091455882346</v>
-      </c>
-      <c r="J62" s="1">
+        <v>-0.36812455268467786</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A63">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K62" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L62" s="1">
-        <f>SIN(2*PI()*B62/$D$4*$D$8)</f>
-        <v>-0.36812455268467786</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A63">
+        <v>48</v>
+      </c>
+      <c r="B63" s="5">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B63">
-        <f>A63/$D$4*1000</f>
-        <v>48</v>
-      </c>
       <c r="C63" s="1">
-        <f>INDEX(J63:L63,1,$D$7)</f>
+        <f>INDEX(I63:K63,1,$D$7)</f>
         <v>-0.24868988716485535</v>
       </c>
       <c r="D63" s="1">
-        <f>D62+$D$10*(C63-D62)</f>
+        <f t="shared" si="7"/>
         <v>-0.46689205556497343</v>
       </c>
       <c r="E63" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>119.43466551982252</v>
       </c>
       <c r="F63" s="1">
-        <f>(D63-D62)*1000</f>
+        <f t="shared" si="8"/>
         <v>99.912887851119564</v>
       </c>
       <c r="G63" s="1">
+        <f t="shared" si="6"/>
+        <v>75.547700329825986</v>
+      </c>
+      <c r="I63" s="1">
+        <f>IF(MOD(A63,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="1">
+        <f>IF(MOD(A63,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K63" s="1">
         <f t="shared" si="2"/>
-        <v>75.547700329825986</v>
-      </c>
-      <c r="J63" s="1">
+        <v>-0.24868988716485535</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A64">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K63" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L63" s="1">
-        <f>SIN(2*PI()*B63/$D$4*$D$8)</f>
-        <v>-0.24868988716485535</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A64">
+        <v>49</v>
+      </c>
+      <c r="B64" s="5">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B64">
-        <f>A64/$D$4*1000</f>
-        <v>49</v>
-      </c>
       <c r="C64" s="1">
-        <f>INDEX(J64:L64,1,$D$7)</f>
+        <f>INDEX(I64:K64,1,$D$7)</f>
         <v>-0.12533323356430465</v>
       </c>
       <c r="D64" s="1">
-        <f>D63+$D$10*(C64-D63)</f>
+        <f t="shared" si="7"/>
         <v>-0.35961600054492576</v>
       </c>
       <c r="E64" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>123.3566536005507</v>
       </c>
       <c r="F64" s="1">
-        <f>(D64-D63)*1000</f>
+        <f t="shared" si="8"/>
         <v>107.27605502004766</v>
       </c>
       <c r="G64" s="1">
+        <f t="shared" si="6"/>
+        <v>85.512873249403341</v>
+      </c>
+      <c r="I64" s="1">
+        <f>IF(MOD(A64,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="1">
+        <f>IF(MOD(A64,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K64" s="1">
         <f t="shared" si="2"/>
-        <v>85.512873249403341</v>
-      </c>
-      <c r="J64" s="1">
+        <v>-0.12533323356430465</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A65">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K64" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L64" s="1">
-        <f>SIN(2*PI()*B64/$D$4*$D$8)</f>
-        <v>-0.12533323356430465</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A65">
+        <v>50</v>
+      </c>
+      <c r="B65" s="5">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B65">
-        <f>A65/$D$4*1000</f>
-        <v>50</v>
-      </c>
       <c r="C65" s="1">
-        <f>INDEX(J65:L65,1,$D$7)</f>
+        <f>INDEX(I65:K65,1,$D$7)</f>
         <v>-2.45029690981724E-16</v>
       </c>
       <c r="D65" s="1">
-        <f>D64+$D$10*(C65-D64)</f>
+        <f t="shared" si="7"/>
         <v>-0.24666858599835789</v>
       </c>
       <c r="E65" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>125.33323356430439</v>
       </c>
       <c r="F65" s="1">
-        <f>(D65-D64)*1000</f>
+        <f t="shared" si="8"/>
         <v>112.94741454656787</v>
       </c>
       <c r="G65" s="1">
+        <f t="shared" si="6"/>
+        <v>94.12945455860644</v>
+      </c>
+      <c r="I65" s="1">
+        <f>IF(MOD(A65,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="J65" s="1">
+        <f>IF(MOD(A65,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K65" s="1">
         <f t="shared" si="2"/>
-        <v>94.12945455860644</v>
-      </c>
-      <c r="J65" s="1">
+        <v>-2.45029690981724E-16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A66">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K65" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L65" s="1">
-        <f>SIN(2*PI()*B65/$D$4*$D$8)</f>
-        <v>-2.45029690981724E-16</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A66">
+        <v>51</v>
+      </c>
+      <c r="B66" s="5">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B66">
-        <f>A66/$D$4*1000</f>
-        <v>51</v>
-      </c>
       <c r="C66" s="1">
-        <f>INDEX(J66:L66,1,$D$7)</f>
+        <f>INDEX(I66:K66,1,$D$7)</f>
         <v>0.12533323356430418</v>
       </c>
       <c r="D66" s="1">
-        <f>D65+$D$10*(C66-D65)</f>
+        <f t="shared" si="7"/>
         <v>-0.1298310602415679</v>
       </c>
       <c r="E66" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>125.33323356430442</v>
       </c>
       <c r="F66" s="1">
-        <f>(D66-D65)*1000</f>
+        <f t="shared" si="8"/>
         <v>116.83752575678999</v>
       </c>
       <c r="G66" s="1">
+        <f t="shared" si="6"/>
+        <v>101.26155637634467</v>
+      </c>
+      <c r="I66" s="1">
+        <f>IF(MOD(A66,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="1">
+        <f>IF(MOD(A66,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K66" s="1">
         <f t="shared" si="2"/>
-        <v>101.26155637634467</v>
-      </c>
-      <c r="J66" s="1">
+        <v>0.12533323356430418</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A67">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K66" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L66" s="1">
-        <f>SIN(2*PI()*B66/$D$4*$D$8)</f>
-        <v>0.12533323356430418</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A67">
+        <v>52</v>
+      </c>
+      <c r="B67" s="5">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B67">
-        <f>A67/$D$4*1000</f>
-        <v>52</v>
-      </c>
       <c r="C67" s="1">
-        <f>INDEX(J67:L67,1,$D$7)</f>
+        <f>INDEX(I67:K67,1,$D$7)</f>
         <v>0.24868988716485574</v>
       </c>
       <c r="D67" s="1">
-        <f>D66+$D$10*(C67-D66)</f>
+        <f t="shared" si="7"/>
         <v>-1.0946020931611039E-2</v>
       </c>
       <c r="E67" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>123.35665360055157</v>
       </c>
       <c r="F67" s="1">
-        <f>(D67-D66)*1000</f>
+        <f t="shared" si="8"/>
         <v>118.88503930995687</v>
       </c>
       <c r="G67" s="1">
+        <f t="shared" si="6"/>
+        <v>106.79670172482977</v>
+      </c>
+      <c r="I67" s="1">
+        <f>IF(MOD(A67,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="1">
+        <f>IF(MOD(A67,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K67" s="1">
         <f t="shared" si="2"/>
-        <v>106.79670172482977</v>
-      </c>
-      <c r="J67" s="1">
+        <v>0.24868988716485574</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A68">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K67" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L67" s="1">
-        <f>SIN(2*PI()*B67/$D$4*$D$8)</f>
-        <v>0.24868988716485574</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A68">
+        <v>53</v>
+      </c>
+      <c r="B68" s="5">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B68">
-        <f>A68/$D$4*1000</f>
-        <v>53</v>
-      </c>
       <c r="C68" s="1">
-        <f>INDEX(J68:L68,1,$D$7)</f>
+        <f>INDEX(I68:K68,1,$D$7)</f>
         <v>0.36812455268467736</v>
       </c>
       <c r="D68" s="1">
-        <f>D67+$D$10*(C68-D67)</f>
+        <f t="shared" si="7"/>
         <v>0.10811164378788597</v>
       </c>
       <c r="E68" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>119.43466551982162</v>
       </c>
       <c r="F68" s="1">
-        <f>(D68-D67)*1000</f>
+        <f t="shared" si="8"/>
         <v>119.05766471949701</v>
       </c>
       <c r="G68" s="1">
+        <f t="shared" si="6"/>
+        <v>110.6475984257562</v>
+      </c>
+      <c r="I68" s="1">
+        <f>IF(MOD(A68,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J68" s="1">
+        <f>IF(MOD(A68,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K68" s="1">
         <f t="shared" si="2"/>
-        <v>110.6475984257562</v>
-      </c>
-      <c r="J68" s="1">
+        <v>0.36812455268467736</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A69">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K68" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L68" s="1">
-        <f>SIN(2*PI()*B68/$D$4*$D$8)</f>
-        <v>0.36812455268467736</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A69">
+        <v>54</v>
+      </c>
+      <c r="B69" s="5">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B69">
-        <f>A69/$D$4*1000</f>
-        <v>54</v>
-      </c>
       <c r="C69" s="1">
-        <f>INDEX(J69:L69,1,$D$7)</f>
+        <f>INDEX(I69:K69,1,$D$7)</f>
         <v>0.48175367410171488</v>
       </c>
       <c r="D69" s="1">
-        <f>D68+$D$10*(C69-D68)</f>
+        <f t="shared" si="7"/>
         <v>0.22546432338481392</v>
       </c>
       <c r="E69" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>113.62912141703751</v>
       </c>
       <c r="F69" s="1">
-        <f>(D69-D68)*1000</f>
+        <f t="shared" si="8"/>
         <v>117.35267959692796</v>
       </c>
       <c r="G69" s="1">
+        <f t="shared" si="6"/>
+        <v>112.75351579723343</v>
+      </c>
+      <c r="I69" s="1">
+        <f>IF(MOD(A69,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J69" s="1">
+        <f>IF(MOD(A69,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K69" s="1">
         <f t="shared" si="2"/>
-        <v>112.75351579723343</v>
-      </c>
-      <c r="J69" s="1">
+        <v>0.48175367410171488</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A70">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K69" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L69" s="1">
-        <f>SIN(2*PI()*B69/$D$4*$D$8)</f>
-        <v>0.48175367410171488</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A70">
+        <v>55</v>
+      </c>
+      <c r="B70" s="5">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B70">
-        <f>A70/$D$4*1000</f>
-        <v>55</v>
-      </c>
       <c r="C70" s="1">
-        <f>INDEX(J70:L70,1,$D$7)</f>
+        <f>INDEX(I70:K70,1,$D$7)</f>
         <v>0.58778525229247358</v>
       </c>
       <c r="D70" s="1">
-        <f>D69+$D$10*(C70-D69)</f>
+        <f t="shared" si="7"/>
         <v>0.33926129597285259</v>
       </c>
       <c r="E70" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>106.03157819075871</v>
       </c>
       <c r="F70" s="1">
-        <f>(D70-D69)*1000</f>
+        <f t="shared" si="8"/>
         <v>113.79697258803867</v>
       </c>
       <c r="G70" s="1">
+        <f t="shared" si="6"/>
+        <v>113.08124244603083</v>
+      </c>
+      <c r="I70" s="1">
+        <f>IF(MOD(A70,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="1">
+        <f>IF(MOD(A70,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K70" s="1">
         <f t="shared" si="2"/>
-        <v>113.08124244603083</v>
-      </c>
-      <c r="J70" s="1">
+        <v>0.58778525229247358</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A71">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K70" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L70" s="1">
-        <f>SIN(2*PI()*B70/$D$4*$D$8)</f>
-        <v>0.58778525229247358</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A71">
+        <v>56</v>
+      </c>
+      <c r="B71" s="5">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B71">
-        <f>A71/$D$4*1000</f>
-        <v>56</v>
-      </c>
       <c r="C71" s="1">
-        <f>INDEX(J71:L71,1,$D$7)</f>
+        <f>INDEX(I71:K71,1,$D$7)</f>
         <v>0.68454710592868795</v>
       </c>
       <c r="D71" s="1">
-        <f>D70+$D$10*(C71-D70)</f>
+        <f t="shared" si="7"/>
         <v>0.44770791529744841</v>
       </c>
       <c r="E71" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>96.761853636214369</v>
       </c>
       <c r="F71" s="1">
-        <f>(D71-D70)*1000</f>
+        <f t="shared" si="8"/>
         <v>108.44661932459582</v>
       </c>
       <c r="G71" s="1">
+        <f t="shared" si="6"/>
+        <v>111.62561005433909</v>
+      </c>
+      <c r="I71" s="1">
+        <f>IF(MOD(A71,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J71" s="1">
+        <f>IF(MOD(A71,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K71" s="1">
         <f t="shared" si="2"/>
-        <v>111.62561005433909</v>
-      </c>
-      <c r="J71" s="1">
+        <v>0.68454710592868795</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A72">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K71" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L71" s="1">
-        <f>SIN(2*PI()*B71/$D$4*$D$8)</f>
-        <v>0.68454710592868795</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A72">
+        <v>57</v>
+      </c>
+      <c r="B72" s="5">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B72">
-        <f>A72/$D$4*1000</f>
-        <v>57</v>
-      </c>
       <c r="C72" s="1">
-        <f>INDEX(J72:L72,1,$D$7)</f>
+        <f>INDEX(I72:K72,1,$D$7)</f>
         <v>0.7705132427757887</v>
       </c>
       <c r="D72" s="1">
-        <f>D71+$D$10*(C72-D71)</f>
+        <f t="shared" si="7"/>
         <v>0.54909391337675761</v>
       </c>
       <c r="E72" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>85.966136847100756</v>
       </c>
       <c r="F72" s="1">
-        <f>(D72-D71)*1000</f>
+        <f t="shared" si="8"/>
         <v>101.3859980793092</v>
       </c>
       <c r="G72" s="1">
+        <f t="shared" si="6"/>
+        <v>108.40957490354712</v>
+      </c>
+      <c r="I72" s="1">
+        <f>IF(MOD(A72,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J72" s="1">
+        <f>IF(MOD(A72,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K72" s="1">
         <f t="shared" si="2"/>
-        <v>108.40957490354712</v>
-      </c>
-      <c r="J72" s="1">
+        <v>0.7705132427757887</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A73">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K72" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L72" s="1">
-        <f>SIN(2*PI()*B72/$D$4*$D$8)</f>
-        <v>0.7705132427757887</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A73">
+        <v>58</v>
+      </c>
+      <c r="B73" s="5">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B73">
-        <f>A73/$D$4*1000</f>
-        <v>58</v>
-      </c>
       <c r="C73" s="1">
-        <f>INDEX(J73:L73,1,$D$7)</f>
+        <f>INDEX(I73:K73,1,$D$7)</f>
         <v>0.84432792550201519</v>
       </c>
       <c r="D73" s="1">
-        <f>D72+$D$10*(C73-D72)</f>
+        <f t="shared" si="7"/>
         <v>0.64182037244762458</v>
       </c>
       <c r="E73" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>73.814682726226494</v>
       </c>
       <c r="F73" s="1">
-        <f>(D73-D72)*1000</f>
+        <f t="shared" si="8"/>
         <v>92.726459070866966</v>
       </c>
       <c r="G73" s="1">
+        <f t="shared" si="6"/>
+        <v>103.48385585141536</v>
+      </c>
+      <c r="I73" s="1">
+        <f>IF(MOD(A73,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J73" s="1">
+        <f>IF(MOD(A73,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K73" s="1">
         <f t="shared" si="2"/>
-        <v>103.48385585141536</v>
-      </c>
-      <c r="J73" s="1">
+        <v>0.84432792550201519</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A74">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K73" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L73" s="1">
-        <f>SIN(2*PI()*B73/$D$4*$D$8)</f>
-        <v>0.84432792550201519</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A74">
+        <v>59</v>
+      </c>
+      <c r="B74" s="5">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B74">
-        <f>A74/$D$4*1000</f>
-        <v>59</v>
-      </c>
       <c r="C74" s="1">
-        <f>INDEX(J74:L74,1,$D$7)</f>
+        <f>INDEX(I74:K74,1,$D$7)</f>
         <v>0.90482705246601935</v>
       </c>
       <c r="D74" s="1">
-        <f>D73+$D$10*(C74-D73)</f>
+        <f t="shared" si="7"/>
         <v>0.72442494085264775</v>
       </c>
       <c r="E74" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>60.499126964004169</v>
       </c>
       <c r="F74" s="1">
-        <f>(D74-D73)*1000</f>
+        <f t="shared" si="8"/>
         <v>82.604568405023173</v>
       </c>
       <c r="G74" s="1">
+        <f t="shared" si="6"/>
+        <v>96.92613447341455</v>
+      </c>
+      <c r="I74" s="1">
+        <f>IF(MOD(A74,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J74" s="1">
+        <f>IF(MOD(A74,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K74" s="1">
         <f t="shared" si="2"/>
-        <v>96.92613447341455</v>
-      </c>
-      <c r="J74" s="1">
+        <v>0.90482705246601935</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A75">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K74" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L74" s="1">
-        <f>SIN(2*PI()*B74/$D$4*$D$8)</f>
-        <v>0.90482705246601935</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A75">
+        <v>60</v>
+      </c>
+      <c r="B75" s="5">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B75">
-        <f>A75/$D$4*1000</f>
-        <v>60</v>
-      </c>
       <c r="C75" s="1">
-        <f>INDEX(J75:L75,1,$D$7)</f>
+        <f>INDEX(I75:K75,1,$D$7)</f>
         <v>0.95105651629515353</v>
       </c>
       <c r="D75" s="1">
-        <f>D74+$D$10*(C75-D74)</f>
+        <f t="shared" si="7"/>
         <v>0.79560489519855748</v>
       </c>
       <c r="E75" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>46.229463829134176</v>
       </c>
       <c r="F75" s="1">
-        <f>(D75-D74)*1000</f>
+        <f t="shared" si="8"/>
         <v>71.179954345909735</v>
       </c>
       <c r="G75" s="1">
+        <f t="shared" si="6"/>
+        <v>88.83982998349903</v>
+      </c>
+      <c r="I75" s="1">
+        <f>IF(MOD(A75,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J75" s="1">
+        <f>IF(MOD(A75,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K75" s="1">
         <f t="shared" si="2"/>
-        <v>88.83982998349903</v>
-      </c>
-      <c r="J75" s="1">
+        <v>0.95105651629515353</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A76">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K75" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L75" s="1">
-        <f>SIN(2*PI()*B75/$D$4*$D$8)</f>
-        <v>0.95105651629515353</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A76">
+        <v>61</v>
+      </c>
+      <c r="B76" s="5">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B76">
-        <f>A76/$D$4*1000</f>
-        <v>61</v>
-      </c>
       <c r="C76" s="1">
-        <f>INDEX(J76:L76,1,$D$7)</f>
+        <f>INDEX(I76:K76,1,$D$7)</f>
         <v>0.98228725072868883</v>
       </c>
       <c r="D76" s="1">
-        <f>D75+$D$10*(C76-D75)</f>
+        <f t="shared" si="7"/>
         <v>0.854237685081769</v>
       </c>
       <c r="E76" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>31.2307344335353</v>
       </c>
       <c r="F76" s="1">
-        <f>(D76-D75)*1000</f>
+        <f t="shared" si="8"/>
         <v>58.632789883211522</v>
       </c>
       <c r="G76" s="1">
+        <f t="shared" si="6"/>
+        <v>79.352468255260945</v>
+      </c>
+      <c r="I76" s="1">
+        <f>IF(MOD(A76,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J76" s="1">
+        <f>IF(MOD(A76,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K76" s="1">
         <f t="shared" si="2"/>
-        <v>79.352468255260945</v>
-      </c>
-      <c r="J76" s="1">
+        <v>0.98228725072868883</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A77">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K76" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L76" s="1">
-        <f>SIN(2*PI()*B76/$D$4*$D$8)</f>
-        <v>0.98228725072868883</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A77">
+        <v>62</v>
+      </c>
+      <c r="B77" s="5">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B77">
-        <f>A77/$D$4*1000</f>
-        <v>62</v>
-      </c>
       <c r="C77" s="1">
-        <f>INDEX(J77:L77,1,$D$7)</f>
+        <f>INDEX(I77:K77,1,$D$7)</f>
         <v>0.99802672842827156</v>
       </c>
       <c r="D77" s="1">
-        <f>D76+$D$10*(C77-D76)</f>
+        <f t="shared" si="7"/>
         <v>0.89939863637843676</v>
       </c>
       <c r="E77" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>15.739477699582727</v>
       </c>
       <c r="F77" s="1">
-        <f>(D77-D76)*1000</f>
+        <f t="shared" si="8"/>
         <v>45.160951296667747</v>
       </c>
       <c r="G77" s="1">
+        <f t="shared" si="6"/>
+        <v>68.613670665480768</v>
+      </c>
+      <c r="I77" s="1">
+        <f>IF(MOD(A77,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J77" s="1">
+        <f>IF(MOD(A77,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K77" s="1">
         <f t="shared" si="2"/>
-        <v>68.613670665480768</v>
-      </c>
-      <c r="J77" s="1">
+        <v>0.99802672842827156</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A78">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K77" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="L77" s="1">
-        <f>SIN(2*PI()*B77/$D$4*$D$8)</f>
-        <v>0.99802672842827156</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A78">
+        <v>63</v>
+      </c>
+      <c r="B78" s="5">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B78">
-        <f>A78/$D$4*1000</f>
-        <v>63</v>
-      </c>
       <c r="C78" s="1">
-        <f>INDEX(J78:L78,1,$D$7)</f>
+        <f>INDEX(I78:K78,1,$D$7)</f>
         <v>0.99802672842827156</v>
       </c>
       <c r="D78" s="1">
-        <f>D77+$D$10*(C78-D77)</f>
+        <f t="shared" si="7"/>
         <v>0.9303755339074945</v>
       </c>
       <c r="E78" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F78" s="1">
-        <f>(D78-D77)*1000</f>
+        <f t="shared" si="8"/>
         <v>30.976897529057744</v>
       </c>
       <c r="G78" s="1">
+        <f t="shared" si="6"/>
+        <v>56.79279447756587</v>
+      </c>
+      <c r="I78" s="1">
+        <f>IF(MOD(A78,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J78" s="1">
+        <f>IF(MOD(A78,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K78" s="1">
         <f t="shared" si="2"/>
-        <v>56.79279447756587</v>
-      </c>
-      <c r="J78" s="1">
+        <v>0.99802672842827156</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A79">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K78" s="1">
+        <v>64</v>
+      </c>
+      <c r="B79" s="5">
+        <f t="shared" ref="B79:B115" si="9">A79/$D$4*1000</f>
+        <v>64</v>
+      </c>
+      <c r="C79" s="1">
+        <f>INDEX(I79:K79,1,$D$7)</f>
+        <v>0.98228725072868861</v>
+      </c>
+      <c r="D79" s="1">
+        <f t="shared" ref="D79:D110" si="10">D78+$D$10*(C79-D78)</f>
+        <v>0.94667985348933403</v>
+      </c>
+      <c r="E79" s="1">
         <f t="shared" si="4"/>
+        <v>-15.739477699582949</v>
+      </c>
+      <c r="F79" s="1">
+        <f t="shared" si="8"/>
+        <v>16.304319581839533</v>
+      </c>
+      <c r="G79" s="1">
+        <f t="shared" si="6"/>
+        <v>44.07626197768726</v>
+      </c>
+      <c r="I79" s="1">
+        <f>IF(MOD(A79,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J79" s="1">
+        <f>IF(MOD(A79,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
         <v>1</v>
       </c>
-      <c r="L78" s="1">
-        <f>SIN(2*PI()*B78/$D$4*$D$8)</f>
-        <v>0.99802672842827156</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A79">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="B79">
-        <f>A79/$D$4*1000</f>
-        <v>64</v>
-      </c>
-      <c r="C79" s="1">
-        <f>INDEX(J79:L79,1,$D$7)</f>
+      <c r="K79" s="1">
+        <f t="shared" ref="K79:K115" si="11">SIN(2*PI()*B79/$D$4*$D$8)</f>
         <v>0.98228725072868861</v>
       </c>
-      <c r="D79" s="1">
-        <f>D78+$D$10*(C79-D78)</f>
-        <v>0.94667985348933403</v>
-      </c>
-      <c r="E79" s="1">
-        <f t="shared" si="1"/>
-        <v>-15.739477699582949</v>
-      </c>
-      <c r="F79" s="1">
-        <f>(D79-D78)*1000</f>
-        <v>16.304319581839533</v>
-      </c>
-      <c r="G79" s="1">
-        <f t="shared" si="2"/>
-        <v>44.07626197768726</v>
-      </c>
-      <c r="J79" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K79" s="1">
-        <f t="shared" si="4"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A80">
+        <f t="shared" ref="A80:A115" si="12">A79+1</f>
+        <v>65</v>
+      </c>
+      <c r="B80" s="5">
+        <f t="shared" si="9"/>
+        <v>65</v>
+      </c>
+      <c r="C80" s="1">
+        <f>INDEX(I80:K80,1,$D$7)</f>
+        <v>0.95105651629515364</v>
+      </c>
+      <c r="D80" s="1">
+        <f t="shared" si="10"/>
+        <v>0.94805446626382239</v>
+      </c>
+      <c r="E80" s="1">
+        <f t="shared" ref="E80:E115" si="13">(C80-C79)*1000</f>
+        <v>-31.23073443353497</v>
+      </c>
+      <c r="F80" s="1">
+        <f t="shared" ref="F80:F115" si="14">(D80-D79)*1000</f>
+        <v>1.3746127744883596</v>
+      </c>
+      <c r="G80" s="1">
+        <f t="shared" ref="G80:G115" si="15">G79+$D$11*(F80-G79)</f>
+        <v>30.664620484907516</v>
+      </c>
+      <c r="I80" s="1">
+        <f>IF(MOD(A80,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J80" s="1">
+        <f>IF(MOD(A80,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
         <v>1</v>
       </c>
-      <c r="L79" s="1">
-        <f>SIN(2*PI()*B79/$D$4*$D$8)</f>
-        <v>0.98228725072868861</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A80">
-        <f t="shared" ref="A80:A115" si="5">A79+1</f>
-        <v>65</v>
-      </c>
-      <c r="B80">
-        <f>A80/$D$4*1000</f>
-        <v>65</v>
-      </c>
-      <c r="C80" s="1">
-        <f>INDEX(J80:L80,1,$D$7)</f>
+      <c r="K80" s="1">
+        <f t="shared" si="11"/>
         <v>0.95105651629515364</v>
       </c>
-      <c r="D80" s="1">
-        <f>D79+$D$10*(C80-D79)</f>
-        <v>0.94805446626382239</v>
-      </c>
-      <c r="E80" s="1">
-        <f t="shared" ref="E80:E115" si="6">(C80-C79)*1000</f>
-        <v>-31.23073443353497</v>
-      </c>
-      <c r="F80" s="1">
-        <f>(D80-D79)*1000</f>
-        <v>1.3746127744883596</v>
-      </c>
-      <c r="G80" s="1">
-        <f t="shared" ref="G80:G115" si="7">G79+$D$11*(F80-G79)</f>
-        <v>30.664620484907516</v>
-      </c>
-      <c r="J80" s="1">
-        <f t="shared" ref="J80:J115" si="8">IF(MOD(A80,FLOOR($D$4/$D$8,1))=0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K80" s="1">
-        <f t="shared" ref="K80:K115" si="9">IF(MOD(A80,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A81">
+        <f t="shared" si="12"/>
+        <v>66</v>
+      </c>
+      <c r="B81" s="5">
+        <f t="shared" si="9"/>
+        <v>66</v>
+      </c>
+      <c r="C81" s="1">
+        <f>INDEX(I81:K81,1,$D$7)</f>
+        <v>0.90482705246601924</v>
+      </c>
+      <c r="D81" s="1">
+        <f t="shared" si="10"/>
+        <v>0.93447769376594081</v>
+      </c>
+      <c r="E81" s="1">
+        <f t="shared" si="13"/>
+        <v>-46.229463829134396</v>
+      </c>
+      <c r="F81" s="1">
+        <f t="shared" si="14"/>
+        <v>-13.576772497881585</v>
+      </c>
+      <c r="G81" s="1">
+        <f t="shared" si="15"/>
+        <v>16.769379600817743</v>
+      </c>
+      <c r="I81" s="1">
+        <f>IF(MOD(A81,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J81" s="1">
+        <f>IF(MOD(A81,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
         <v>1</v>
       </c>
-      <c r="L80" s="1">
-        <f>SIN(2*PI()*B80/$D$4*$D$8)</f>
-        <v>0.95105651629515364</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A81">
-        <f t="shared" si="5"/>
-        <v>66</v>
-      </c>
-      <c r="B81">
-        <f>A81/$D$4*1000</f>
-        <v>66</v>
-      </c>
-      <c r="C81" s="1">
-        <f>INDEX(J81:L81,1,$D$7)</f>
+      <c r="K81" s="1">
+        <f t="shared" si="11"/>
         <v>0.90482705246601924</v>
       </c>
-      <c r="D81" s="1">
-        <f>D80+$D$10*(C81-D80)</f>
-        <v>0.93447769376594081</v>
-      </c>
-      <c r="E81" s="1">
-        <f t="shared" si="6"/>
-        <v>-46.229463829134396</v>
-      </c>
-      <c r="F81" s="1">
-        <f>(D81-D80)*1000</f>
-        <v>-13.576772497881585</v>
-      </c>
-      <c r="G81" s="1">
-        <f t="shared" si="7"/>
-        <v>16.769379600817743</v>
-      </c>
-      <c r="J81" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K81" s="1">
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A82">
+        <f t="shared" si="12"/>
+        <v>67</v>
+      </c>
+      <c r="B82" s="5">
         <f t="shared" si="9"/>
+        <v>67</v>
+      </c>
+      <c r="C82" s="1">
+        <f>INDEX(I82:K82,1,$D$7)</f>
+        <v>0.84432792550201508</v>
+      </c>
+      <c r="D82" s="1">
+        <f t="shared" si="10"/>
+        <v>0.90616364980807018</v>
+      </c>
+      <c r="E82" s="1">
+        <f t="shared" si="13"/>
+        <v>-60.499126964004169</v>
+      </c>
+      <c r="F82" s="1">
+        <f t="shared" si="14"/>
+        <v>-28.314043957870627</v>
+      </c>
+      <c r="G82" s="1">
+        <f t="shared" si="15"/>
+        <v>2.6096755772323217</v>
+      </c>
+      <c r="I82" s="1">
+        <f>IF(MOD(A82,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J82" s="1">
+        <f>IF(MOD(A82,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
         <v>1</v>
       </c>
-      <c r="L81" s="1">
-        <f>SIN(2*PI()*B81/$D$4*$D$8)</f>
-        <v>0.90482705246601924</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A82">
-        <f t="shared" si="5"/>
-        <v>67</v>
-      </c>
-      <c r="B82">
-        <f>A82/$D$4*1000</f>
-        <v>67</v>
-      </c>
-      <c r="C82" s="1">
-        <f>INDEX(J82:L82,1,$D$7)</f>
+      <c r="K82" s="1">
+        <f t="shared" si="11"/>
         <v>0.84432792550201508</v>
       </c>
-      <c r="D82" s="1">
-        <f>D81+$D$10*(C82-D81)</f>
-        <v>0.90616364980807018</v>
-      </c>
-      <c r="E82" s="1">
-        <f t="shared" si="6"/>
-        <v>-60.499126964004169</v>
-      </c>
-      <c r="F82" s="1">
-        <f>(D82-D81)*1000</f>
-        <v>-28.314043957870627</v>
-      </c>
-      <c r="G82" s="1">
-        <f t="shared" si="7"/>
-        <v>2.6096755772323217</v>
-      </c>
-      <c r="J82" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K82" s="1">
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A83">
+        <f t="shared" si="12"/>
+        <v>68</v>
+      </c>
+      <c r="B83" s="5">
         <f t="shared" si="9"/>
+        <v>68</v>
+      </c>
+      <c r="C83" s="1">
+        <f>INDEX(I83:K83,1,$D$7)</f>
+        <v>0.7705132427757897</v>
+      </c>
+      <c r="D83" s="1">
+        <f t="shared" si="10"/>
+        <v>0.8635588637772228</v>
+      </c>
+      <c r="E83" s="1">
+        <f t="shared" si="13"/>
+        <v>-73.814682726225385</v>
+      </c>
+      <c r="F83" s="1">
+        <f t="shared" si="14"/>
+        <v>-42.604786030847386</v>
+      </c>
+      <c r="G83" s="1">
+        <f t="shared" si="15"/>
+        <v>-11.591184593086144</v>
+      </c>
+      <c r="I83" s="1">
+        <f>IF(MOD(A83,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J83" s="1">
+        <f>IF(MOD(A83,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
         <v>1</v>
       </c>
-      <c r="L82" s="1">
-        <f>SIN(2*PI()*B82/$D$4*$D$8)</f>
-        <v>0.84432792550201508</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A83">
-        <f t="shared" si="5"/>
-        <v>68</v>
-      </c>
-      <c r="B83">
-        <f>A83/$D$4*1000</f>
-        <v>68</v>
-      </c>
-      <c r="C83" s="1">
-        <f>INDEX(J83:L83,1,$D$7)</f>
+      <c r="K83" s="1">
+        <f t="shared" si="11"/>
         <v>0.7705132427757897</v>
       </c>
-      <c r="D83" s="1">
-        <f>D82+$D$10*(C83-D82)</f>
-        <v>0.8635588637772228</v>
-      </c>
-      <c r="E83" s="1">
-        <f t="shared" si="6"/>
-        <v>-73.814682726225385</v>
-      </c>
-      <c r="F83" s="1">
-        <f>(D83-D82)*1000</f>
-        <v>-42.604786030847386</v>
-      </c>
-      <c r="G83" s="1">
-        <f t="shared" si="7"/>
-        <v>-11.591184593086144</v>
-      </c>
-      <c r="J83" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K83" s="1">
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A84">
+        <f t="shared" si="12"/>
+        <v>69</v>
+      </c>
+      <c r="B84" s="5">
         <f t="shared" si="9"/>
+        <v>69</v>
+      </c>
+      <c r="C84" s="1">
+        <f>INDEX(I84:K84,1,$D$7)</f>
+        <v>0.68454710592868839</v>
+      </c>
+      <c r="D84" s="1">
+        <f t="shared" si="10"/>
+        <v>0.80733523859983758</v>
+      </c>
+      <c r="E84" s="1">
+        <f t="shared" si="13"/>
+        <v>-85.966136847101311</v>
+      </c>
+      <c r="F84" s="1">
+        <f t="shared" si="14"/>
+        <v>-56.223625177385216</v>
+      </c>
+      <c r="G84" s="1">
+        <f t="shared" si="15"/>
+        <v>-25.60924486087481</v>
+      </c>
+      <c r="I84" s="1">
+        <f>IF(MOD(A84,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J84" s="1">
+        <f>IF(MOD(A84,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
         <v>1</v>
       </c>
-      <c r="L83" s="1">
-        <f>SIN(2*PI()*B83/$D$4*$D$8)</f>
-        <v>0.7705132427757897</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A84">
-        <f t="shared" si="5"/>
-        <v>69</v>
-      </c>
-      <c r="B84">
-        <f>A84/$D$4*1000</f>
-        <v>69</v>
-      </c>
-      <c r="C84" s="1">
-        <f>INDEX(J84:L84,1,$D$7)</f>
+      <c r="K84" s="1">
+        <f t="shared" si="11"/>
         <v>0.68454710592868839</v>
       </c>
-      <c r="D84" s="1">
-        <f>D83+$D$10*(C84-D83)</f>
-        <v>0.80733523859983758</v>
-      </c>
-      <c r="E84" s="1">
-        <f t="shared" si="6"/>
-        <v>-85.966136847101311</v>
-      </c>
-      <c r="F84" s="1">
-        <f>(D84-D83)*1000</f>
-        <v>-56.223625177385216</v>
-      </c>
-      <c r="G84" s="1">
-        <f t="shared" si="7"/>
-        <v>-25.60924486087481</v>
-      </c>
-      <c r="J84" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K84" s="1">
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A85">
+        <f t="shared" si="12"/>
+        <v>70</v>
+      </c>
+      <c r="B85" s="5">
         <f t="shared" si="9"/>
+        <v>70</v>
+      </c>
+      <c r="C85" s="1">
+        <f>INDEX(I85:K85,1,$D$7)</f>
+        <v>0.58778525229247336</v>
+      </c>
+      <c r="D85" s="1">
+        <f t="shared" si="10"/>
+        <v>0.7383794544312372</v>
+      </c>
+      <c r="E85" s="1">
+        <f t="shared" si="13"/>
+        <v>-96.761853636215037</v>
+      </c>
+      <c r="F85" s="1">
+        <f t="shared" si="14"/>
+        <v>-68.955784168600374</v>
+      </c>
+      <c r="G85" s="1">
+        <f t="shared" si="15"/>
+        <v>-39.223432040894778</v>
+      </c>
+      <c r="I85" s="1">
+        <f>IF(MOD(A85,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J85" s="1">
+        <f>IF(MOD(A85,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
         <v>1</v>
       </c>
-      <c r="L84" s="1">
-        <f>SIN(2*PI()*B84/$D$4*$D$8)</f>
-        <v>0.68454710592868839</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A85">
-        <f t="shared" si="5"/>
-        <v>70</v>
-      </c>
-      <c r="B85">
-        <f>A85/$D$4*1000</f>
-        <v>70</v>
-      </c>
-      <c r="C85" s="1">
-        <f>INDEX(J85:L85,1,$D$7)</f>
+      <c r="K85" s="1">
+        <f t="shared" si="11"/>
         <v>0.58778525229247336</v>
       </c>
-      <c r="D85" s="1">
-        <f>D84+$D$10*(C85-D84)</f>
-        <v>0.7383794544312372</v>
-      </c>
-      <c r="E85" s="1">
-        <f t="shared" si="6"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A86">
+        <f t="shared" si="12"/>
+        <v>71</v>
+      </c>
+      <c r="B86" s="5">
+        <f t="shared" si="9"/>
+        <v>71</v>
+      </c>
+      <c r="C86" s="1">
+        <f>INDEX(I86:K86,1,$D$7)</f>
+        <v>0.48175367410171621</v>
+      </c>
+      <c r="D86" s="1">
+        <f t="shared" si="10"/>
+        <v>0.65777898517988687</v>
+      </c>
+      <c r="E86" s="1">
+        <f t="shared" si="13"/>
+        <v>-106.03157819075714</v>
+      </c>
+      <c r="F86" s="1">
+        <f t="shared" si="14"/>
+        <v>-80.600469251350333</v>
+      </c>
+      <c r="G86" s="1">
+        <f t="shared" si="15"/>
+        <v>-52.219042268016061</v>
+      </c>
+      <c r="I86" s="1">
+        <f>IF(MOD(A86,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J86" s="1">
+        <f>IF(MOD(A86,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K86" s="1">
+        <f t="shared" si="11"/>
+        <v>0.48175367410171621</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A87">
+        <f t="shared" si="12"/>
+        <v>72</v>
+      </c>
+      <c r="B87" s="5">
+        <f t="shared" si="9"/>
+        <v>72</v>
+      </c>
+      <c r="C87" s="1">
+        <f>INDEX(I87:K87,1,$D$7)</f>
+        <v>0.36812455268467797</v>
+      </c>
+      <c r="D87" s="1">
+        <f t="shared" si="10"/>
+        <v>0.56680494839422346</v>
+      </c>
+      <c r="E87" s="1">
+        <f t="shared" si="13"/>
+        <v>-113.62912141703823</v>
+      </c>
+      <c r="F87" s="1">
+        <f t="shared" si="14"/>
+        <v>-90.974036785663401</v>
+      </c>
+      <c r="G87" s="1">
+        <f t="shared" si="15"/>
+        <v>-64.39112700535199</v>
+      </c>
+      <c r="I87" s="1">
+        <f>IF(MOD(A87,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J87" s="1">
+        <f>IF(MOD(A87,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K87" s="1">
+        <f t="shared" si="11"/>
+        <v>0.36812455268467797</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A88">
+        <f t="shared" si="12"/>
+        <v>73</v>
+      </c>
+      <c r="B88" s="5">
+        <f t="shared" si="9"/>
+        <v>73</v>
+      </c>
+      <c r="C88" s="1">
+        <f>INDEX(I88:K88,1,$D$7)</f>
+        <v>0.24868988716485549</v>
+      </c>
+      <c r="D88" s="1">
+        <f t="shared" si="10"/>
+        <v>0.46689205897958352</v>
+      </c>
+      <c r="E88" s="1">
+        <f t="shared" si="13"/>
+        <v>-119.43466551982249</v>
+      </c>
+      <c r="F88" s="1">
+        <f t="shared" si="14"/>
+        <v>-99.912889414639935</v>
+      </c>
+      <c r="G88" s="1">
+        <f t="shared" si="15"/>
+        <v>-75.547725205062292</v>
+      </c>
+      <c r="I88" s="1">
+        <f>IF(MOD(A88,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J88" s="1">
+        <f>IF(MOD(A88,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K88" s="1">
+        <f t="shared" si="11"/>
+        <v>0.24868988716485549</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A89">
+        <f t="shared" si="12"/>
+        <v>74</v>
+      </c>
+      <c r="B89" s="5">
+        <f t="shared" si="9"/>
+        <v>74</v>
+      </c>
+      <c r="C89" s="1">
+        <f>INDEX(I89:K89,1,$D$7)</f>
+        <v>0.1253332335643039</v>
+      </c>
+      <c r="D89" s="1">
+        <f t="shared" si="10"/>
+        <v>0.35961600288708229</v>
+      </c>
+      <c r="E89" s="1">
+        <f t="shared" si="13"/>
+        <v>-123.3566536005516</v>
+      </c>
+      <c r="F89" s="1">
+        <f t="shared" si="14"/>
+        <v>-107.27605609250124</v>
+      </c>
+      <c r="G89" s="1">
+        <f t="shared" si="15"/>
+        <v>-85.51289064871321</v>
+      </c>
+      <c r="I89" s="1">
+        <f>IF(MOD(A89,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J89" s="1">
+        <f>IF(MOD(A89,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K89" s="1">
+        <f t="shared" si="11"/>
+        <v>0.1253332335643039</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A90">
+        <f t="shared" si="12"/>
+        <v>75</v>
+      </c>
+      <c r="B90" s="5">
+        <f t="shared" si="9"/>
+        <v>75</v>
+      </c>
+      <c r="C90" s="1">
+        <f>INDEX(I90:K90,1,$D$7)</f>
+        <v>3.67544536472586E-16</v>
+      </c>
+      <c r="D90" s="1">
+        <f t="shared" si="10"/>
+        <v>0.24666858760489502</v>
+      </c>
+      <c r="E90" s="1">
+        <f t="shared" si="13"/>
+        <v>-125.33323356430354</v>
+      </c>
+      <c r="F90" s="1">
+        <f t="shared" si="14"/>
+        <v>-112.94741528218727</v>
+      </c>
+      <c r="G90" s="1">
+        <f t="shared" si="15"/>
+        <v>-94.129466724220507</v>
+      </c>
+      <c r="I90" s="1">
+        <f>IF(MOD(A90,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J90" s="1">
+        <f>IF(MOD(A90,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K90" s="1">
+        <f t="shared" si="11"/>
+        <v>3.67544536472586E-16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A91">
+        <f t="shared" si="12"/>
+        <v>76</v>
+      </c>
+      <c r="B91" s="5">
+        <f t="shared" si="9"/>
+        <v>76</v>
+      </c>
+      <c r="C91" s="1">
+        <f>INDEX(I91:K91,1,$D$7)</f>
+        <v>-0.12533323356430318</v>
+      </c>
+      <c r="D91" s="1">
+        <f t="shared" si="10"/>
+        <v>0.12983106134352765</v>
+      </c>
+      <c r="E91" s="1">
+        <f t="shared" si="13"/>
+        <v>-125.33323356430354</v>
+      </c>
+      <c r="F91" s="1">
+        <f t="shared" si="14"/>
+        <v>-116.83752626136737</v>
+      </c>
+      <c r="G91" s="1">
+        <f t="shared" si="15"/>
+        <v>-101.26156487948559</v>
+      </c>
+      <c r="I91" s="1">
+        <f>IF(MOD(A91,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J91" s="1">
+        <f>IF(MOD(A91,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K91" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.12533323356430318</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A92">
+        <f t="shared" si="12"/>
+        <v>77</v>
+      </c>
+      <c r="B92" s="5">
+        <f t="shared" si="9"/>
+        <v>77</v>
+      </c>
+      <c r="C92" s="1">
+        <f>INDEX(I92:K92,1,$D$7)</f>
+        <v>-0.24868988716485477</v>
+      </c>
+      <c r="D92" s="1">
+        <f t="shared" si="10"/>
+        <v>1.0946021687469942E-2</v>
+      </c>
+      <c r="E92" s="1">
+        <f t="shared" si="13"/>
+        <v>-123.3566536005516</v>
+      </c>
+      <c r="F92" s="1">
+        <f t="shared" si="14"/>
+        <v>-118.8850396560577</v>
+      </c>
+      <c r="G92" s="1">
+        <f t="shared" si="15"/>
+        <v>-106.79670766602521</v>
+      </c>
+      <c r="I92" s="1">
+        <f>IF(MOD(A92,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J92" s="1">
+        <f>IF(MOD(A92,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K92" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.24868988716485477</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A93">
+        <f t="shared" si="12"/>
+        <v>78</v>
+      </c>
+      <c r="B93" s="5">
+        <f t="shared" si="9"/>
+        <v>78</v>
+      </c>
+      <c r="C93" s="1">
+        <f>INDEX(I93:K93,1,$D$7)</f>
+        <v>-0.36812455268467725</v>
+      </c>
+      <c r="D93" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.10811164326942557</v>
+      </c>
+      <c r="E93" s="1">
+        <f t="shared" si="13"/>
+        <v>-119.43466551982249</v>
+      </c>
+      <c r="F93" s="1">
+        <f t="shared" si="14"/>
+        <v>-119.05766495689551</v>
+      </c>
+      <c r="G93" s="1">
+        <f t="shared" si="15"/>
+        <v>-110.64760257551545</v>
+      </c>
+      <c r="I93" s="1">
+        <f>IF(MOD(A93,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J93" s="1">
+        <f>IF(MOD(A93,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K93" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.36812455268467725</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A94">
+        <f t="shared" si="12"/>
+        <v>79</v>
+      </c>
+      <c r="B94" s="5">
+        <f t="shared" si="9"/>
+        <v>79</v>
+      </c>
+      <c r="C94" s="1">
+        <f>INDEX(I94:K94,1,$D$7)</f>
+        <v>-0.48175367410171555</v>
+      </c>
+      <c r="D94" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.22546432302919067</v>
+      </c>
+      <c r="E94" s="1">
+        <f t="shared" si="13"/>
+        <v>-113.62912141703829</v>
+      </c>
+      <c r="F94" s="1">
+        <f t="shared" si="14"/>
+        <v>-117.3526797597651</v>
+      </c>
+      <c r="G94" s="1">
+        <f t="shared" si="15"/>
+        <v>-112.75351869478882</v>
+      </c>
+      <c r="I94" s="1">
+        <f>IF(MOD(A94,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J94" s="1">
+        <f>IF(MOD(A94,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K94" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.48175367410171555</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A95">
+        <f t="shared" si="12"/>
+        <v>80</v>
+      </c>
+      <c r="B95" s="5">
+        <f t="shared" si="9"/>
+        <v>80</v>
+      </c>
+      <c r="C95" s="1">
+        <f>INDEX(I95:K95,1,$D$7)</f>
+        <v>-0.5877852522924728</v>
+      </c>
+      <c r="D95" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.33926129572892244</v>
+      </c>
+      <c r="E95" s="1">
+        <f t="shared" si="13"/>
+        <v>-106.03157819075726</v>
+      </c>
+      <c r="F95" s="1">
+        <f t="shared" si="14"/>
+        <v>-113.79697269973177</v>
+      </c>
+      <c r="G95" s="1">
+        <f t="shared" si="15"/>
+        <v>-113.08124446860862</v>
+      </c>
+      <c r="I95" s="1">
+        <f>IF(MOD(A95,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J95" s="1">
+        <f>IF(MOD(A95,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K95" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.5877852522924728</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A96">
+        <f t="shared" si="12"/>
+        <v>81</v>
+      </c>
+      <c r="B96" s="5">
+        <f t="shared" si="9"/>
+        <v>81</v>
+      </c>
+      <c r="C96" s="1">
+        <f>INDEX(I96:K96,1,$D$7)</f>
+        <v>-0.68454710592868784</v>
+      </c>
+      <c r="D96" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.44770791513013131</v>
+      </c>
+      <c r="E96" s="1">
+        <f t="shared" si="13"/>
         <v>-96.761853636215037</v>
       </c>
-      <c r="F85" s="1">
-        <f>(D85-D84)*1000</f>
-        <v>-68.955784168600374</v>
-      </c>
-      <c r="G85" s="1">
-        <f t="shared" si="7"/>
-        <v>-39.223432040894778</v>
-      </c>
-      <c r="J85" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K85" s="1">
+      <c r="F96" s="1">
+        <f t="shared" si="14"/>
+        <v>-108.44661940120886</v>
+      </c>
+      <c r="G96" s="1">
+        <f t="shared" si="15"/>
+        <v>-111.62561146573249</v>
+      </c>
+      <c r="I96" s="1">
+        <f>IF(MOD(A96,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J96" s="1">
+        <f>IF(MOD(A96,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K96" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.68454710592868784</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A97">
+        <f t="shared" si="12"/>
+        <v>82</v>
+      </c>
+      <c r="B97" s="5">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="L85" s="1">
-        <f>SIN(2*PI()*B85/$D$4*$D$8)</f>
-        <v>0.58778525229247336</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A86">
-        <f t="shared" si="5"/>
-        <v>71</v>
-      </c>
-      <c r="B86">
-        <f>A86/$D$4*1000</f>
-        <v>71</v>
-      </c>
-      <c r="C86" s="1">
-        <f>INDEX(J86:L86,1,$D$7)</f>
-        <v>0.48175367410171621</v>
-      </c>
-      <c r="D86" s="1">
-        <f>D85+$D$10*(C86-D85)</f>
-        <v>0.65777898517988687</v>
-      </c>
-      <c r="E86" s="1">
-        <f t="shared" si="6"/>
-        <v>-106.03157819075714</v>
-      </c>
-      <c r="F86" s="1">
-        <f>(D86-D85)*1000</f>
-        <v>-80.600469251350333</v>
-      </c>
-      <c r="G86" s="1">
-        <f t="shared" si="7"/>
-        <v>-52.219042268016061</v>
-      </c>
-      <c r="J86" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K86" s="1">
+        <v>82</v>
+      </c>
+      <c r="C97" s="1">
+        <f>INDEX(I97:K97,1,$D$7)</f>
+        <v>-0.77051324277578803</v>
+      </c>
+      <c r="D97" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.54909391326199097</v>
+      </c>
+      <c r="E97" s="1">
+        <f t="shared" si="13"/>
+        <v>-85.966136847100188</v>
+      </c>
+      <c r="F97" s="1">
+        <f t="shared" si="14"/>
+        <v>-101.38599813185967</v>
+      </c>
+      <c r="G97" s="1">
+        <f t="shared" si="15"/>
+        <v>-108.40957588815809</v>
+      </c>
+      <c r="I97" s="1">
+        <f>IF(MOD(A97,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J97" s="1">
+        <f>IF(MOD(A97,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K97" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.77051324277578803</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A98">
+        <f t="shared" si="12"/>
+        <v>83</v>
+      </c>
+      <c r="B98" s="5">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="L86" s="1">
-        <f>SIN(2*PI()*B86/$D$4*$D$8)</f>
-        <v>0.48175367410171621</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A87">
-        <f t="shared" si="5"/>
-        <v>72</v>
-      </c>
-      <c r="B87">
-        <f>A87/$D$4*1000</f>
-        <v>72</v>
-      </c>
-      <c r="C87" s="1">
-        <f>INDEX(J87:L87,1,$D$7)</f>
-        <v>0.36812455268467797</v>
-      </c>
-      <c r="D87" s="1">
-        <f>D86+$D$10*(C87-D86)</f>
-        <v>0.56680494839422346</v>
-      </c>
-      <c r="E87" s="1">
-        <f t="shared" si="6"/>
-        <v>-113.62912141703823</v>
-      </c>
-      <c r="F87" s="1">
-        <f>(D87-D86)*1000</f>
-        <v>-90.974036785663401</v>
-      </c>
-      <c r="G87" s="1">
-        <f t="shared" si="7"/>
-        <v>-64.39112700535199</v>
-      </c>
-      <c r="J87" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K87" s="1">
+        <v>83</v>
+      </c>
+      <c r="C98" s="1">
+        <f>INDEX(I98:K98,1,$D$7)</f>
+        <v>-0.84432792550201563</v>
+      </c>
+      <c r="D98" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.64182037236890377</v>
+      </c>
+      <c r="E98" s="1">
+        <f t="shared" si="13"/>
+        <v>-73.814682726227602</v>
+      </c>
+      <c r="F98" s="1">
+        <f t="shared" si="14"/>
+        <v>-92.726459106912799</v>
+      </c>
+      <c r="G98" s="1">
+        <f t="shared" si="15"/>
+        <v>-103.48385653810304</v>
+      </c>
+      <c r="I98" s="1">
+        <f>IF(MOD(A98,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J98" s="1">
+        <f>IF(MOD(A98,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K98" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.84432792550201563</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A99">
+        <f t="shared" si="12"/>
+        <v>84</v>
+      </c>
+      <c r="B99" s="5">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="L87" s="1">
-        <f>SIN(2*PI()*B87/$D$4*$D$8)</f>
-        <v>0.36812455268467797</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A88">
-        <f t="shared" si="5"/>
-        <v>73</v>
-      </c>
-      <c r="B88">
-        <f>A88/$D$4*1000</f>
-        <v>73</v>
-      </c>
-      <c r="C88" s="1">
-        <f>INDEX(J88:L88,1,$D$7)</f>
-        <v>0.24868988716485549</v>
-      </c>
-      <c r="D88" s="1">
-        <f>D87+$D$10*(C88-D87)</f>
-        <v>0.46689205897958352</v>
-      </c>
-      <c r="E88" s="1">
-        <f t="shared" si="6"/>
-        <v>-119.43466551982249</v>
-      </c>
-      <c r="F88" s="1">
-        <f>(D88-D87)*1000</f>
-        <v>-99.912889414639935</v>
-      </c>
-      <c r="G88" s="1">
-        <f t="shared" si="7"/>
-        <v>-75.547725205062292</v>
-      </c>
-      <c r="J88" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K88" s="1">
+        <v>84</v>
+      </c>
+      <c r="C99" s="1">
+        <f>INDEX(I99:K99,1,$D$7)</f>
+        <v>-0.90482705246601969</v>
+      </c>
+      <c r="D99" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.7244249407986515</v>
+      </c>
+      <c r="E99" s="1">
+        <f t="shared" si="13"/>
+        <v>-60.499126964004056</v>
+      </c>
+      <c r="F99" s="1">
+        <f t="shared" si="14"/>
+        <v>-82.604568429747729</v>
+      </c>
+      <c r="G99" s="1">
+        <f t="shared" si="15"/>
+        <v>-96.926134952194289</v>
+      </c>
+      <c r="I99" s="1">
+        <f>IF(MOD(A99,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J99" s="1">
+        <f>IF(MOD(A99,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K99" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.90482705246601969</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A100">
+        <f t="shared" si="12"/>
+        <v>85</v>
+      </c>
+      <c r="B100" s="5">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="L88" s="1">
-        <f>SIN(2*PI()*B88/$D$4*$D$8)</f>
-        <v>0.24868988716485549</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A89">
-        <f t="shared" si="5"/>
-        <v>74</v>
-      </c>
-      <c r="B89">
-        <f>A89/$D$4*1000</f>
-        <v>74</v>
-      </c>
-      <c r="C89" s="1">
-        <f>INDEX(J89:L89,1,$D$7)</f>
-        <v>0.1253332335643039</v>
-      </c>
-      <c r="D89" s="1">
-        <f>D88+$D$10*(C89-D88)</f>
-        <v>0.35961600288708229</v>
-      </c>
-      <c r="E89" s="1">
-        <f t="shared" si="6"/>
-        <v>-123.3566536005516</v>
-      </c>
-      <c r="F89" s="1">
-        <f>(D89-D88)*1000</f>
-        <v>-107.27605609250124</v>
-      </c>
-      <c r="G89" s="1">
-        <f t="shared" si="7"/>
-        <v>-85.51289064871321</v>
-      </c>
-      <c r="J89" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K89" s="1">
+        <v>85</v>
+      </c>
+      <c r="C100" s="1">
+        <f>INDEX(I100:K100,1,$D$7)</f>
+        <v>-0.95105651629515342</v>
+      </c>
+      <c r="D100" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.79560489516152033</v>
+      </c>
+      <c r="E100" s="1">
+        <f t="shared" si="13"/>
+        <v>-46.229463829133735</v>
+      </c>
+      <c r="F100" s="1">
+        <f t="shared" si="14"/>
+        <v>-71.179954362868841</v>
+      </c>
+      <c r="G100" s="1">
+        <f t="shared" si="15"/>
+        <v>-88.839830317231147</v>
+      </c>
+      <c r="I100" s="1">
+        <f>IF(MOD(A100,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J100" s="1">
+        <f>IF(MOD(A100,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K100" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.95105651629515342</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A101">
+        <f t="shared" si="12"/>
+        <v>86</v>
+      </c>
+      <c r="B101" s="5">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="L89" s="1">
-        <f>SIN(2*PI()*B89/$D$4*$D$8)</f>
-        <v>0.1253332335643039</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A90">
-        <f t="shared" si="5"/>
-        <v>75</v>
-      </c>
-      <c r="B90">
-        <f>A90/$D$4*1000</f>
-        <v>75</v>
-      </c>
-      <c r="C90" s="1">
-        <f>INDEX(J90:L90,1,$D$7)</f>
-        <v>3.67544536472586E-16</v>
-      </c>
-      <c r="D90" s="1">
-        <f>D89+$D$10*(C90-D89)</f>
-        <v>0.24666858760489502</v>
-      </c>
-      <c r="E90" s="1">
-        <f t="shared" si="6"/>
-        <v>-125.33323356430354</v>
-      </c>
-      <c r="F90" s="1">
-        <f>(D90-D89)*1000</f>
-        <v>-112.94741528218727</v>
-      </c>
-      <c r="G90" s="1">
-        <f t="shared" si="7"/>
-        <v>-94.129466724220507</v>
-      </c>
-      <c r="J90" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K90" s="1">
+        <v>86</v>
+      </c>
+      <c r="C101" s="1">
+        <f>INDEX(I101:K101,1,$D$7)</f>
+        <v>-0.98228725072868883</v>
+      </c>
+      <c r="D101" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.85423768505636444</v>
+      </c>
+      <c r="E101" s="1">
+        <f t="shared" si="13"/>
+        <v>-31.23073443353541</v>
+      </c>
+      <c r="F101" s="1">
+        <f t="shared" si="14"/>
+        <v>-58.632789894844109</v>
+      </c>
+      <c r="G101" s="1">
+        <f t="shared" si="15"/>
+        <v>-79.352468487828745</v>
+      </c>
+      <c r="I101" s="1">
+        <f>IF(MOD(A101,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J101" s="1">
+        <f>IF(MOD(A101,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K101" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.98228725072868883</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A102">
+        <f t="shared" si="12"/>
+        <v>87</v>
+      </c>
+      <c r="B102" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L90" s="1">
-        <f>SIN(2*PI()*B90/$D$4*$D$8)</f>
-        <v>3.67544536472586E-16</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A91">
-        <f t="shared" si="5"/>
-        <v>76</v>
-      </c>
-      <c r="B91">
-        <f>A91/$D$4*1000</f>
-        <v>76</v>
-      </c>
-      <c r="C91" s="1">
-        <f>INDEX(J91:L91,1,$D$7)</f>
-        <v>-0.12533323356430318</v>
-      </c>
-      <c r="D91" s="1">
-        <f>D90+$D$10*(C91-D90)</f>
-        <v>0.12983106134352765</v>
-      </c>
-      <c r="E91" s="1">
-        <f t="shared" si="6"/>
-        <v>-125.33323356430354</v>
-      </c>
-      <c r="F91" s="1">
-        <f>(D91-D90)*1000</f>
-        <v>-116.83752626136737</v>
-      </c>
-      <c r="G91" s="1">
-        <f t="shared" si="7"/>
-        <v>-101.26156487948559</v>
-      </c>
-      <c r="J91" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K91" s="1">
+        <v>87</v>
+      </c>
+      <c r="C102" s="1">
+        <f>INDEX(I102:K102,1,$D$7)</f>
+        <v>-0.99802672842827145</v>
+      </c>
+      <c r="D102" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.89939863636101125</v>
+      </c>
+      <c r="E102" s="1">
+        <f t="shared" si="13"/>
+        <v>-15.739477699582615</v>
+      </c>
+      <c r="F102" s="1">
+        <f t="shared" si="14"/>
+        <v>-45.160951304646815</v>
+      </c>
+      <c r="G102" s="1">
+        <f t="shared" si="15"/>
+        <v>-68.613670827510234</v>
+      </c>
+      <c r="I102" s="1">
+        <f>IF(MOD(A102,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J102" s="1">
+        <f>IF(MOD(A102,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K102" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.99802672842827145</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A103">
+        <f t="shared" si="12"/>
+        <v>88</v>
+      </c>
+      <c r="B103" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L91" s="1">
-        <f>SIN(2*PI()*B91/$D$4*$D$8)</f>
-        <v>-0.12533323356430318</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A92">
-        <f t="shared" si="5"/>
-        <v>77</v>
-      </c>
-      <c r="B92">
-        <f>A92/$D$4*1000</f>
-        <v>77</v>
-      </c>
-      <c r="C92" s="1">
-        <f>INDEX(J92:L92,1,$D$7)</f>
-        <v>-0.24868988716485477</v>
-      </c>
-      <c r="D92" s="1">
-        <f>D91+$D$10*(C92-D91)</f>
-        <v>1.0946021687469942E-2</v>
-      </c>
-      <c r="E92" s="1">
-        <f t="shared" si="6"/>
-        <v>-123.3566536005516</v>
-      </c>
-      <c r="F92" s="1">
-        <f>(D92-D91)*1000</f>
-        <v>-118.8850396560577</v>
-      </c>
-      <c r="G92" s="1">
-        <f t="shared" si="7"/>
-        <v>-106.79670766602521</v>
-      </c>
-      <c r="J92" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K92" s="1">
+        <v>88</v>
+      </c>
+      <c r="C103" s="1">
+        <f>INDEX(I103:K103,1,$D$7)</f>
+        <v>-0.99802672842827167</v>
+      </c>
+      <c r="D103" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.93037553389554206</v>
+      </c>
+      <c r="E103" s="1">
+        <f t="shared" si="13"/>
+        <v>-2.2204460492503131E-13</v>
+      </c>
+      <c r="F103" s="1">
+        <f t="shared" si="14"/>
+        <v>-30.976897534530814</v>
+      </c>
+      <c r="G103" s="1">
+        <f t="shared" si="15"/>
+        <v>-56.792794590424442</v>
+      </c>
+      <c r="I103" s="1">
+        <f>IF(MOD(A103,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J103" s="1">
+        <f>IF(MOD(A103,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K103" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.99802672842827167</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A104">
+        <f t="shared" si="12"/>
+        <v>89</v>
+      </c>
+      <c r="B104" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L92" s="1">
-        <f>SIN(2*PI()*B92/$D$4*$D$8)</f>
-        <v>-0.24868988716485477</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A93">
-        <f t="shared" si="5"/>
-        <v>78</v>
-      </c>
-      <c r="B93">
-        <f>A93/$D$4*1000</f>
-        <v>78</v>
-      </c>
-      <c r="C93" s="1">
-        <f>INDEX(J93:L93,1,$D$7)</f>
-        <v>-0.36812455268467725</v>
-      </c>
-      <c r="D93" s="1">
-        <f>D92+$D$10*(C93-D92)</f>
-        <v>-0.10811164326942557</v>
-      </c>
-      <c r="E93" s="1">
-        <f t="shared" si="6"/>
-        <v>-119.43466551982249</v>
-      </c>
-      <c r="F93" s="1">
-        <f>(D93-D92)*1000</f>
-        <v>-119.05766495689551</v>
-      </c>
-      <c r="G93" s="1">
-        <f t="shared" si="7"/>
-        <v>-110.64760257551545</v>
-      </c>
-      <c r="J93" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K93" s="1">
+        <v>89</v>
+      </c>
+      <c r="C104" s="1">
+        <f>INDEX(I104:K104,1,$D$7)</f>
+        <v>-0.98228725072868861</v>
+      </c>
+      <c r="D104" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.94667985348113559</v>
+      </c>
+      <c r="E104" s="1">
+        <f t="shared" si="13"/>
+        <v>15.739477699583059</v>
+      </c>
+      <c r="F104" s="1">
+        <f t="shared" si="14"/>
+        <v>-16.304319585593529</v>
+      </c>
+      <c r="G104" s="1">
+        <f t="shared" si="15"/>
+        <v>-44.076262056278502</v>
+      </c>
+      <c r="I104" s="1">
+        <f>IF(MOD(A104,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J104" s="1">
+        <f>IF(MOD(A104,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K104" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.98228725072868861</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A105">
+        <f t="shared" si="12"/>
+        <v>90</v>
+      </c>
+      <c r="B105" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L93" s="1">
-        <f>SIN(2*PI()*B93/$D$4*$D$8)</f>
-        <v>-0.36812455268467725</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A94">
-        <f t="shared" si="5"/>
-        <v>79</v>
-      </c>
-      <c r="B94">
-        <f>A94/$D$4*1000</f>
-        <v>79</v>
-      </c>
-      <c r="C94" s="1">
-        <f>INDEX(J94:L94,1,$D$7)</f>
-        <v>-0.48175367410171555</v>
-      </c>
-      <c r="D94" s="1">
-        <f>D93+$D$10*(C94-D93)</f>
-        <v>-0.22546432302919067</v>
-      </c>
-      <c r="E94" s="1">
-        <f t="shared" si="6"/>
-        <v>-113.62912141703829</v>
-      </c>
-      <c r="F94" s="1">
-        <f>(D94-D93)*1000</f>
-        <v>-117.3526797597651</v>
-      </c>
-      <c r="G94" s="1">
-        <f t="shared" si="7"/>
-        <v>-112.75351869478882</v>
-      </c>
-      <c r="J94" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K94" s="1">
+        <v>90</v>
+      </c>
+      <c r="C105" s="1">
+        <f>INDEX(I105:K105,1,$D$7)</f>
+        <v>-0.95105651629515375</v>
+      </c>
+      <c r="D105" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.94805446625819889</v>
+      </c>
+      <c r="E105" s="1">
+        <f t="shared" si="13"/>
+        <v>31.230734433534856</v>
+      </c>
+      <c r="F105" s="1">
+        <f t="shared" si="14"/>
+        <v>-1.3746127770632999</v>
+      </c>
+      <c r="G105" s="1">
+        <f t="shared" si="15"/>
+        <v>-30.664620539623723</v>
+      </c>
+      <c r="I105" s="1">
+        <f>IF(MOD(A105,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J105" s="1">
+        <f>IF(MOD(A105,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K105" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.95105651629515375</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A106">
+        <f t="shared" si="12"/>
+        <v>91</v>
+      </c>
+      <c r="B106" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L94" s="1">
-        <f>SIN(2*PI()*B94/$D$4*$D$8)</f>
-        <v>-0.48175367410171555</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A95">
-        <f t="shared" si="5"/>
-        <v>80</v>
-      </c>
-      <c r="B95">
-        <f>A95/$D$4*1000</f>
-        <v>80</v>
-      </c>
-      <c r="C95" s="1">
-        <f>INDEX(J95:L95,1,$D$7)</f>
-        <v>-0.5877852522924728</v>
-      </c>
-      <c r="D95" s="1">
-        <f>D94+$D$10*(C95-D94)</f>
-        <v>-0.33926129572892244</v>
-      </c>
-      <c r="E95" s="1">
-        <f t="shared" si="6"/>
-        <v>-106.03157819075726</v>
-      </c>
-      <c r="F95" s="1">
-        <f>(D95-D94)*1000</f>
-        <v>-113.79697269973177</v>
-      </c>
-      <c r="G95" s="1">
-        <f t="shared" si="7"/>
-        <v>-113.08124446860862</v>
-      </c>
-      <c r="J95" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K95" s="1">
+        <v>91</v>
+      </c>
+      <c r="C106" s="1">
+        <f>INDEX(I106:K106,1,$D$7)</f>
+        <v>-0.90482705246602002</v>
+      </c>
+      <c r="D106" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.93447769376208378</v>
+      </c>
+      <c r="E106" s="1">
+        <f t="shared" si="13"/>
+        <v>46.229463829133735</v>
+      </c>
+      <c r="F106" s="1">
+        <f t="shared" si="14"/>
+        <v>13.576772496115108</v>
+      </c>
+      <c r="G106" s="1">
+        <f t="shared" si="15"/>
+        <v>-16.769379638903615</v>
+      </c>
+      <c r="I106" s="1">
+        <f>IF(MOD(A106,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J106" s="1">
+        <f>IF(MOD(A106,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K106" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.90482705246602002</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A107">
+        <f t="shared" si="12"/>
+        <v>92</v>
+      </c>
+      <c r="B107" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L95" s="1">
-        <f>SIN(2*PI()*B95/$D$4*$D$8)</f>
-        <v>-0.5877852522924728</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A96">
-        <f t="shared" si="5"/>
-        <v>81</v>
-      </c>
-      <c r="B96">
-        <f>A96/$D$4*1000</f>
-        <v>81</v>
-      </c>
-      <c r="C96" s="1">
-        <f>INDEX(J96:L96,1,$D$7)</f>
-        <v>-0.68454710592868784</v>
-      </c>
-      <c r="D96" s="1">
-        <f>D95+$D$10*(C96-D95)</f>
-        <v>-0.44770791513013131</v>
-      </c>
-      <c r="E96" s="1">
-        <f t="shared" si="6"/>
-        <v>-96.761853636215037</v>
-      </c>
-      <c r="F96" s="1">
-        <f>(D96-D95)*1000</f>
-        <v>-108.44661940120886</v>
-      </c>
-      <c r="G96" s="1">
-        <f t="shared" si="7"/>
-        <v>-111.62561146573249</v>
-      </c>
-      <c r="J96" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K96" s="1">
+        <v>92</v>
+      </c>
+      <c r="C107" s="1">
+        <f>INDEX(I107:K107,1,$D$7)</f>
+        <v>-0.84432792550201508</v>
+      </c>
+      <c r="D107" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.90616364980542452</v>
+      </c>
+      <c r="E107" s="1">
+        <f t="shared" si="13"/>
+        <v>60.499126964004944</v>
+      </c>
+      <c r="F107" s="1">
+        <f t="shared" si="14"/>
+        <v>28.314043956659262</v>
+      </c>
+      <c r="G107" s="1">
+        <f t="shared" si="15"/>
+        <v>-2.6096756037367275</v>
+      </c>
+      <c r="I107" s="1">
+        <f>IF(MOD(A107,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J107" s="1">
+        <f>IF(MOD(A107,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K107" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.84432792550201508</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A108">
+        <f t="shared" si="12"/>
+        <v>93</v>
+      </c>
+      <c r="B108" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L96" s="1">
-        <f>SIN(2*PI()*B96/$D$4*$D$8)</f>
-        <v>-0.68454710592868784</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A97">
-        <f t="shared" si="5"/>
-        <v>82</v>
-      </c>
-      <c r="B97">
-        <f>A97/$D$4*1000</f>
-        <v>82</v>
-      </c>
-      <c r="C97" s="1">
-        <f>INDEX(J97:L97,1,$D$7)</f>
-        <v>-0.77051324277578803</v>
-      </c>
-      <c r="D97" s="1">
-        <f>D96+$D$10*(C97-D96)</f>
-        <v>-0.54909391326199097</v>
-      </c>
-      <c r="E97" s="1">
-        <f t="shared" si="6"/>
-        <v>-85.966136847100188</v>
-      </c>
-      <c r="F97" s="1">
-        <f>(D97-D96)*1000</f>
-        <v>-101.38599813185967</v>
-      </c>
-      <c r="G97" s="1">
-        <f t="shared" si="7"/>
-        <v>-108.40957588815809</v>
-      </c>
-      <c r="J97" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K97" s="1">
+        <v>93</v>
+      </c>
+      <c r="C108" s="1">
+        <f>INDEX(I108:K108,1,$D$7)</f>
+        <v>-0.7705132427757897</v>
+      </c>
+      <c r="D108" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.86355886377540803</v>
+      </c>
+      <c r="E108" s="1">
+        <f t="shared" si="13"/>
+        <v>73.814682726225385</v>
+      </c>
+      <c r="F108" s="1">
+        <f t="shared" si="14"/>
+        <v>42.604786030016498</v>
+      </c>
+      <c r="G108" s="1">
+        <f t="shared" si="15"/>
+        <v>11.59118457464522</v>
+      </c>
+      <c r="I108" s="1">
+        <f>IF(MOD(A108,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J108" s="1">
+        <f>IF(MOD(A108,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K108" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.7705132427757897</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A109">
+        <f t="shared" si="12"/>
+        <v>94</v>
+      </c>
+      <c r="B109" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L97" s="1">
-        <f>SIN(2*PI()*B97/$D$4*$D$8)</f>
-        <v>-0.77051324277578803</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A98">
-        <f t="shared" si="5"/>
-        <v>83</v>
-      </c>
-      <c r="B98">
-        <f>A98/$D$4*1000</f>
-        <v>83</v>
-      </c>
-      <c r="C98" s="1">
-        <f>INDEX(J98:L98,1,$D$7)</f>
-        <v>-0.84432792550201563</v>
-      </c>
-      <c r="D98" s="1">
-        <f>D97+$D$10*(C98-D97)</f>
-        <v>-0.64182037236890377</v>
-      </c>
-      <c r="E98" s="1">
-        <f t="shared" si="6"/>
-        <v>-73.814682726227602</v>
-      </c>
-      <c r="F98" s="1">
-        <f>(D98-D97)*1000</f>
-        <v>-92.726459106912799</v>
-      </c>
-      <c r="G98" s="1">
-        <f t="shared" si="7"/>
-        <v>-103.48385653810304</v>
-      </c>
-      <c r="J98" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K98" s="1">
+        <v>94</v>
+      </c>
+      <c r="C109" s="1">
+        <f>INDEX(I109:K109,1,$D$7)</f>
+        <v>-0.6845471059286885</v>
+      </c>
+      <c r="D109" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.8073352385985928</v>
+      </c>
+      <c r="E109" s="1">
+        <f t="shared" si="13"/>
+        <v>85.966136847101197</v>
+      </c>
+      <c r="F109" s="1">
+        <f t="shared" si="14"/>
+        <v>56.223625176815226</v>
+      </c>
+      <c r="G109" s="1">
+        <f t="shared" si="15"/>
+        <v>25.60924484804675</v>
+      </c>
+      <c r="I109" s="1">
+        <f>IF(MOD(A109,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J109" s="1">
+        <f>IF(MOD(A109,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K109" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.6845471059286885</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A110">
+        <f t="shared" si="12"/>
+        <v>95</v>
+      </c>
+      <c r="B110" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L98" s="1">
-        <f>SIN(2*PI()*B98/$D$4*$D$8)</f>
-        <v>-0.84432792550201563</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A99">
-        <f t="shared" si="5"/>
-        <v>84</v>
-      </c>
-      <c r="B99">
-        <f>A99/$D$4*1000</f>
-        <v>84</v>
-      </c>
-      <c r="C99" s="1">
-        <f>INDEX(J99:L99,1,$D$7)</f>
-        <v>-0.90482705246601969</v>
-      </c>
-      <c r="D99" s="1">
-        <f>D98+$D$10*(C99-D98)</f>
-        <v>-0.7244249407986515</v>
-      </c>
-      <c r="E99" s="1">
-        <f t="shared" si="6"/>
-        <v>-60.499126964004056</v>
-      </c>
-      <c r="F99" s="1">
-        <f>(D99-D98)*1000</f>
-        <v>-82.604568429747729</v>
-      </c>
-      <c r="G99" s="1">
-        <f t="shared" si="7"/>
-        <v>-96.926134952194289</v>
-      </c>
-      <c r="J99" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K99" s="1">
+        <v>95</v>
+      </c>
+      <c r="C110" s="1">
+        <f>INDEX(I110:K110,1,$D$7)</f>
+        <v>-0.58778525229247203</v>
+      </c>
+      <c r="D110" s="1">
+        <f t="shared" si="10"/>
+        <v>-0.738379454430383</v>
+      </c>
+      <c r="E110" s="1">
+        <f t="shared" si="13"/>
+        <v>96.761853636216472</v>
+      </c>
+      <c r="F110" s="1">
+        <f t="shared" si="14"/>
+        <v>68.955784168209803</v>
+      </c>
+      <c r="G110" s="1">
+        <f t="shared" si="15"/>
+        <v>39.223432031973054</v>
+      </c>
+      <c r="I110" s="1">
+        <f>IF(MOD(A110,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J110" s="1">
+        <f>IF(MOD(A110,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K110" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.58778525229247203</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A111">
+        <f t="shared" si="12"/>
+        <v>96</v>
+      </c>
+      <c r="B111" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L99" s="1">
-        <f>SIN(2*PI()*B99/$D$4*$D$8)</f>
-        <v>-0.90482705246601969</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A100">
-        <f t="shared" si="5"/>
-        <v>85</v>
-      </c>
-      <c r="B100">
-        <f>A100/$D$4*1000</f>
-        <v>85</v>
-      </c>
-      <c r="C100" s="1">
-        <f>INDEX(J100:L100,1,$D$7)</f>
-        <v>-0.95105651629515342</v>
-      </c>
-      <c r="D100" s="1">
-        <f>D99+$D$10*(C100-D99)</f>
-        <v>-0.79560489516152033</v>
-      </c>
-      <c r="E100" s="1">
-        <f t="shared" si="6"/>
-        <v>-46.229463829133735</v>
-      </c>
-      <c r="F100" s="1">
-        <f>(D100-D99)*1000</f>
-        <v>-71.179954362868841</v>
-      </c>
-      <c r="G100" s="1">
-        <f t="shared" si="7"/>
-        <v>-88.839830317231147</v>
-      </c>
-      <c r="J100" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K100" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L100" s="1">
-        <f>SIN(2*PI()*B100/$D$4*$D$8)</f>
-        <v>-0.95105651629515342</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A101">
-        <f t="shared" si="5"/>
-        <v>86</v>
-      </c>
-      <c r="B101">
-        <f>A101/$D$4*1000</f>
-        <v>86</v>
-      </c>
-      <c r="C101" s="1">
-        <f>INDEX(J101:L101,1,$D$7)</f>
-        <v>-0.98228725072868883</v>
-      </c>
-      <c r="D101" s="1">
-        <f>D100+$D$10*(C101-D100)</f>
-        <v>-0.85423768505636444</v>
-      </c>
-      <c r="E101" s="1">
-        <f t="shared" si="6"/>
-        <v>-31.23073443353541</v>
-      </c>
-      <c r="F101" s="1">
-        <f>(D101-D100)*1000</f>
-        <v>-58.632789894844109</v>
-      </c>
-      <c r="G101" s="1">
-        <f t="shared" si="7"/>
-        <v>-79.352468487828745</v>
-      </c>
-      <c r="J101" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K101" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L101" s="1">
-        <f>SIN(2*PI()*B101/$D$4*$D$8)</f>
-        <v>-0.98228725072868883</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A102">
-        <f t="shared" si="5"/>
-        <v>87</v>
-      </c>
-      <c r="B102">
-        <f>A102/$D$4*1000</f>
-        <v>87</v>
-      </c>
-      <c r="C102" s="1">
-        <f>INDEX(J102:L102,1,$D$7)</f>
-        <v>-0.99802672842827145</v>
-      </c>
-      <c r="D102" s="1">
-        <f>D101+$D$10*(C102-D101)</f>
-        <v>-0.89939863636101125</v>
-      </c>
-      <c r="E102" s="1">
-        <f t="shared" si="6"/>
-        <v>-15.739477699582615</v>
-      </c>
-      <c r="F102" s="1">
-        <f>(D102-D101)*1000</f>
-        <v>-45.160951304646815</v>
-      </c>
-      <c r="G102" s="1">
-        <f t="shared" si="7"/>
-        <v>-68.613670827510234</v>
-      </c>
-      <c r="J102" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K102" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L102" s="1">
-        <f>SIN(2*PI()*B102/$D$4*$D$8)</f>
-        <v>-0.99802672842827145</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A103">
-        <f t="shared" si="5"/>
-        <v>88</v>
-      </c>
-      <c r="B103">
-        <f>A103/$D$4*1000</f>
-        <v>88</v>
-      </c>
-      <c r="C103" s="1">
-        <f>INDEX(J103:L103,1,$D$7)</f>
-        <v>-0.99802672842827167</v>
-      </c>
-      <c r="D103" s="1">
-        <f>D102+$D$10*(C103-D102)</f>
-        <v>-0.93037553389554206</v>
-      </c>
-      <c r="E103" s="1">
-        <f t="shared" si="6"/>
-        <v>-2.2204460492503131E-13</v>
-      </c>
-      <c r="F103" s="1">
-        <f>(D103-D102)*1000</f>
-        <v>-30.976897534530814</v>
-      </c>
-      <c r="G103" s="1">
-        <f t="shared" si="7"/>
-        <v>-56.792794590424442</v>
-      </c>
-      <c r="J103" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K103" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L103" s="1">
-        <f>SIN(2*PI()*B103/$D$4*$D$8)</f>
-        <v>-0.99802672842827167</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A104">
-        <f t="shared" si="5"/>
-        <v>89</v>
-      </c>
-      <c r="B104">
-        <f>A104/$D$4*1000</f>
-        <v>89</v>
-      </c>
-      <c r="C104" s="1">
-        <f>INDEX(J104:L104,1,$D$7)</f>
-        <v>-0.98228725072868861</v>
-      </c>
-      <c r="D104" s="1">
-        <f>D103+$D$10*(C104-D103)</f>
-        <v>-0.94667985348113559</v>
-      </c>
-      <c r="E104" s="1">
-        <f t="shared" si="6"/>
-        <v>15.739477699583059</v>
-      </c>
-      <c r="F104" s="1">
-        <f>(D104-D103)*1000</f>
-        <v>-16.304319585593529</v>
-      </c>
-      <c r="G104" s="1">
-        <f t="shared" si="7"/>
-        <v>-44.076262056278502</v>
-      </c>
-      <c r="J104" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K104" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L104" s="1">
-        <f>SIN(2*PI()*B104/$D$4*$D$8)</f>
-        <v>-0.98228725072868861</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A105">
-        <f t="shared" si="5"/>
-        <v>90</v>
-      </c>
-      <c r="B105">
-        <f>A105/$D$4*1000</f>
-        <v>90</v>
-      </c>
-      <c r="C105" s="1">
-        <f>INDEX(J105:L105,1,$D$7)</f>
-        <v>-0.95105651629515375</v>
-      </c>
-      <c r="D105" s="1">
-        <f>D104+$D$10*(C105-D104)</f>
-        <v>-0.94805446625819889</v>
-      </c>
-      <c r="E105" s="1">
-        <f t="shared" si="6"/>
-        <v>31.230734433534856</v>
-      </c>
-      <c r="F105" s="1">
-        <f>(D105-D104)*1000</f>
-        <v>-1.3746127770632999</v>
-      </c>
-      <c r="G105" s="1">
-        <f t="shared" si="7"/>
-        <v>-30.664620539623723</v>
-      </c>
-      <c r="J105" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K105" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L105" s="1">
-        <f>SIN(2*PI()*B105/$D$4*$D$8)</f>
-        <v>-0.95105651629515375</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A106">
-        <f t="shared" si="5"/>
-        <v>91</v>
-      </c>
-      <c r="B106">
-        <f>A106/$D$4*1000</f>
-        <v>91</v>
-      </c>
-      <c r="C106" s="1">
-        <f>INDEX(J106:L106,1,$D$7)</f>
-        <v>-0.90482705246602002</v>
-      </c>
-      <c r="D106" s="1">
-        <f>D105+$D$10*(C106-D105)</f>
-        <v>-0.93447769376208378</v>
-      </c>
-      <c r="E106" s="1">
-        <f t="shared" si="6"/>
-        <v>46.229463829133735</v>
-      </c>
-      <c r="F106" s="1">
-        <f>(D106-D105)*1000</f>
-        <v>13.576772496115108</v>
-      </c>
-      <c r="G106" s="1">
-        <f t="shared" si="7"/>
-        <v>-16.769379638903615</v>
-      </c>
-      <c r="J106" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K106" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L106" s="1">
-        <f>SIN(2*PI()*B106/$D$4*$D$8)</f>
-        <v>-0.90482705246602002</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A107">
-        <f t="shared" si="5"/>
-        <v>92</v>
-      </c>
-      <c r="B107">
-        <f>A107/$D$4*1000</f>
-        <v>92</v>
-      </c>
-      <c r="C107" s="1">
-        <f>INDEX(J107:L107,1,$D$7)</f>
-        <v>-0.84432792550201508</v>
-      </c>
-      <c r="D107" s="1">
-        <f>D106+$D$10*(C107-D106)</f>
-        <v>-0.90616364980542452</v>
-      </c>
-      <c r="E107" s="1">
-        <f t="shared" si="6"/>
-        <v>60.499126964004944</v>
-      </c>
-      <c r="F107" s="1">
-        <f>(D107-D106)*1000</f>
-        <v>28.314043956659262</v>
-      </c>
-      <c r="G107" s="1">
-        <f t="shared" si="7"/>
-        <v>-2.6096756037367275</v>
-      </c>
-      <c r="J107" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K107" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L107" s="1">
-        <f>SIN(2*PI()*B107/$D$4*$D$8)</f>
-        <v>-0.84432792550201508</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A108">
-        <f t="shared" si="5"/>
-        <v>93</v>
-      </c>
-      <c r="B108">
-        <f>A108/$D$4*1000</f>
-        <v>93</v>
-      </c>
-      <c r="C108" s="1">
-        <f>INDEX(J108:L108,1,$D$7)</f>
-        <v>-0.7705132427757897</v>
-      </c>
-      <c r="D108" s="1">
-        <f>D107+$D$10*(C108-D107)</f>
-        <v>-0.86355886377540803</v>
-      </c>
-      <c r="E108" s="1">
-        <f t="shared" si="6"/>
-        <v>73.814682726225385</v>
-      </c>
-      <c r="F108" s="1">
-        <f>(D108-D107)*1000</f>
-        <v>42.604786030016498</v>
-      </c>
-      <c r="G108" s="1">
-        <f t="shared" si="7"/>
-        <v>11.59118457464522</v>
-      </c>
-      <c r="J108" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K108" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L108" s="1">
-        <f>SIN(2*PI()*B108/$D$4*$D$8)</f>
-        <v>-0.7705132427757897</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A109">
-        <f t="shared" si="5"/>
-        <v>94</v>
-      </c>
-      <c r="B109">
-        <f>A109/$D$4*1000</f>
-        <v>94</v>
-      </c>
-      <c r="C109" s="1">
-        <f>INDEX(J109:L109,1,$D$7)</f>
-        <v>-0.6845471059286885</v>
-      </c>
-      <c r="D109" s="1">
-        <f>D108+$D$10*(C109-D108)</f>
-        <v>-0.8073352385985928</v>
-      </c>
-      <c r="E109" s="1">
-        <f t="shared" si="6"/>
-        <v>85.966136847101197</v>
-      </c>
-      <c r="F109" s="1">
-        <f>(D109-D108)*1000</f>
-        <v>56.223625176815226</v>
-      </c>
-      <c r="G109" s="1">
-        <f t="shared" si="7"/>
-        <v>25.60924484804675</v>
-      </c>
-      <c r="J109" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K109" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L109" s="1">
-        <f>SIN(2*PI()*B109/$D$4*$D$8)</f>
-        <v>-0.6845471059286885</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A110">
-        <f t="shared" si="5"/>
-        <v>95</v>
-      </c>
-      <c r="B110">
-        <f>A110/$D$4*1000</f>
-        <v>95</v>
-      </c>
-      <c r="C110" s="1">
-        <f>INDEX(J110:L110,1,$D$7)</f>
-        <v>-0.58778525229247203</v>
-      </c>
-      <c r="D110" s="1">
-        <f>D109+$D$10*(C110-D109)</f>
-        <v>-0.738379454430383</v>
-      </c>
-      <c r="E110" s="1">
-        <f t="shared" si="6"/>
-        <v>96.761853636216472</v>
-      </c>
-      <c r="F110" s="1">
-        <f>(D110-D109)*1000</f>
-        <v>68.955784168209803</v>
-      </c>
-      <c r="G110" s="1">
-        <f t="shared" si="7"/>
-        <v>39.223432031973054</v>
-      </c>
-      <c r="J110" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K110" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L110" s="1">
-        <f>SIN(2*PI()*B110/$D$4*$D$8)</f>
-        <v>-0.58778525229247203</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A111">
-        <f t="shared" si="5"/>
         <v>96</v>
       </c>
-      <c r="B111">
-        <f>A111/$D$4*1000</f>
-        <v>96</v>
-      </c>
       <c r="C111" s="1">
-        <f>INDEX(J111:L111,1,$D$7)</f>
+        <f>INDEX(I111:K111,1,$D$7)</f>
         <v>-0.48175367410171632</v>
       </c>
       <c r="D111" s="1">
@@ -10473,41 +10523,41 @@
         <v>-0.657778985179301</v>
       </c>
       <c r="E111" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>106.03157819075571</v>
       </c>
       <c r="F111" s="1">
-        <f>(D111-D110)*1000</f>
+        <f t="shared" si="14"/>
         <v>80.600469251081989</v>
       </c>
       <c r="G111" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>52.219042261812177</v>
       </c>
+      <c r="I111" s="1">
+        <f>IF(MOD(A111,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
       <c r="J111" s="1">
-        <f t="shared" si="8"/>
+        <f>IF(MOD(A111,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
         <v>0</v>
       </c>
       <c r="K111" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.48175367410171632</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A112">
+        <f t="shared" si="12"/>
+        <v>97</v>
+      </c>
+      <c r="B112" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L111" s="1">
-        <f>SIN(2*PI()*B111/$D$4*$D$8)</f>
-        <v>-0.48175367410171632</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A112">
-        <f t="shared" si="5"/>
         <v>97</v>
       </c>
-      <c r="B112">
-        <f>A112/$D$4*1000</f>
-        <v>97</v>
-      </c>
       <c r="C112" s="1">
-        <f>INDEX(J112:L112,1,$D$7)</f>
+        <f>INDEX(I112:K112,1,$D$7)</f>
         <v>-0.3681245526846797</v>
       </c>
       <c r="D112" s="1">
@@ -10515,41 +10565,41 @@
         <v>-0.56680494839382212</v>
       </c>
       <c r="E112" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>113.62912141703663</v>
       </c>
       <c r="F112" s="1">
-        <f>(D112-D111)*1000</f>
+        <f t="shared" si="14"/>
         <v>90.974036785478887</v>
       </c>
       <c r="G112" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>64.391127001038669</v>
       </c>
+      <c r="I112" s="1">
+        <f>IF(MOD(A112,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
       <c r="J112" s="1">
-        <f t="shared" si="8"/>
+        <f>IF(MOD(A112,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
         <v>0</v>
       </c>
       <c r="K112" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.3681245526846797</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A113">
+        <f t="shared" si="12"/>
+        <v>98</v>
+      </c>
+      <c r="B113" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L112" s="1">
-        <f>SIN(2*PI()*B112/$D$4*$D$8)</f>
-        <v>-0.3681245526846797</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A113">
-        <f t="shared" si="5"/>
         <v>98</v>
       </c>
-      <c r="B113">
-        <f>A113/$D$4*1000</f>
-        <v>98</v>
-      </c>
       <c r="C113" s="1">
-        <f>INDEX(J113:L113,1,$D$7)</f>
+        <f>INDEX(I113:K113,1,$D$7)</f>
         <v>-0.2486898871648556</v>
       </c>
       <c r="D113" s="1">
@@ -10557,41 +10607,41 @@
         <v>-0.46689205897930824</v>
       </c>
       <c r="E113" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>119.43466551982409</v>
       </c>
       <c r="F113" s="1">
-        <f>(D113-D112)*1000</f>
+        <f t="shared" si="14"/>
         <v>99.91288941451387</v>
       </c>
       <c r="G113" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>75.5477252020641</v>
       </c>
+      <c r="I113" s="1">
+        <f>IF(MOD(A113,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
       <c r="J113" s="1">
-        <f t="shared" si="8"/>
+        <f>IF(MOD(A113,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
         <v>0</v>
       </c>
       <c r="K113" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.2486898871648556</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A114">
+        <f t="shared" si="12"/>
+        <v>99</v>
+      </c>
+      <c r="B114" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L113" s="1">
-        <f>SIN(2*PI()*B113/$D$4*$D$8)</f>
-        <v>-0.2486898871648556</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A114">
-        <f t="shared" si="5"/>
         <v>99</v>
       </c>
-      <c r="B114">
-        <f>A114/$D$4*1000</f>
-        <v>99</v>
-      </c>
       <c r="C114" s="1">
-        <f>INDEX(J114:L114,1,$D$7)</f>
+        <f>INDEX(I114:K114,1,$D$7)</f>
         <v>-0.12533323356430401</v>
       </c>
       <c r="D114" s="1">
@@ -10599,41 +10649,41 @@
         <v>-0.35961600288689349</v>
       </c>
       <c r="E114" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>123.3566536005516</v>
       </c>
       <c r="F114" s="1">
-        <f>(D114-D113)*1000</f>
+        <f t="shared" si="14"/>
         <v>107.27605609241475</v>
       </c>
       <c r="G114" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>85.512890646629515</v>
       </c>
+      <c r="I114" s="1">
+        <f>IF(MOD(A114,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>0</v>
+      </c>
       <c r="J114" s="1">
-        <f t="shared" si="8"/>
+        <f>IF(MOD(A114,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
         <v>0</v>
       </c>
       <c r="K114" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.12533323356430401</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A115">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+      <c r="B115" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L114" s="1">
-        <f>SIN(2*PI()*B114/$D$4*$D$8)</f>
-        <v>-0.12533323356430401</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A115">
-        <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="B115">
-        <f>A115/$D$4*1000</f>
-        <v>100</v>
-      </c>
       <c r="C115" s="1">
-        <f>INDEX(J115:L115,1,$D$7)</f>
+        <f>INDEX(I115:K115,1,$D$7)</f>
         <v>-4.90059381963448E-16</v>
       </c>
       <c r="D115" s="1">
@@ -10641,27 +10691,27 @@
         <v>-0.24666858760476557</v>
       </c>
       <c r="E115" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>125.33323356430351</v>
       </c>
       <c r="F115" s="1">
-        <f>(D115-D114)*1000</f>
+        <f t="shared" si="14"/>
         <v>112.94741528212793</v>
       </c>
       <c r="G115" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>94.129466722772619</v>
       </c>
+      <c r="I115" s="1">
+        <f>IF(MOD(A115,FLOOR($D$4/$D$8,1))=0,1,0)</f>
+        <v>1</v>
+      </c>
       <c r="J115" s="1">
-        <f t="shared" si="8"/>
+        <f>IF(MOD(A115,FLOOR($D$4/$D$8,1))&lt;FLOOR($D$4/$D$8,1)/2,1,0)</f>
         <v>1</v>
       </c>
       <c r="K115" s="1">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="L115" s="1">
-        <f>SIN(2*PI()*B115/$D$4*$D$8)</f>
+        <f t="shared" si="11"/>
         <v>-4.90059381963448E-16</v>
       </c>
     </row>
